--- a/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Rekap" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Lingkungan &amp; Akun" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Matriks Stasiun" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sudah Diketahui" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Catatan &amp; Batasan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$4:$R$269</definedName>
@@ -898,7 +898,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Tingkat 1+2 TIDAK membuktikan ke-18 stasiun berperilaku benar pada setiap cabang. Ke-18 stasiun punya service, Form, dan Data Preview-nya sendiri-sendiri, jadi bug di satu stasiun tidak mengatakan apa pun tentang yang lain. Tiga defek yang ditemukan pada 2026-10-08 semuanya hanya ada di SATU stasiun. Melewatkan Tingkat 3 adalah keputusan risiko, bukan penghematan gratis.</t>
+          <t>Tingkat 1+2 TIDAK membuktikan ke-18 stasiun berperilaku benar pada setiap cabang. Setiap stasiun punya layar dan aturannya sendiri, jadi hasil baik di satu stasiun tidak menjamin stasiun lain — dan temuan yang pernah ada memang hanya muncul di satu stasiun, bukan di semuanya. Melewatkan Tingkat 3 adalah keputusan risiko, bukan penghematan gratis.</t>
         </is>
       </c>
       <c r="C21" s="6" t="n"/>
@@ -912,7 +912,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Pangkas waktu PENYIAPAN, bukan cakupan. backend/database/seeders/BrowserTestFixtureSeeder.php sudah membuat satu mill, satu Production Line dengan stasiun aktif untuk SETIAP jenis, "PL Tanpa &lt;Station&gt;" per keluarga (prasyarat MB-FORM-15 dan WB-FRM-07), serta akun keempat peran. Jalankan e2e-web/scripts/prepare-db.sh lalu uji di basis data itu — banyak langkah "Siapkan…" langsung gugur, dan cakupannya tidak berkurang sedikit pun.</t>
+          <t>Pangkas waktu PENYIAPAN, bukan cakupan. Minta tim pengembang menyiapkan satu basis data uji berisi data contoh: dua mill, Production Line dengan stasiun aktif untuk setiap jenis, satu Production Line yang sengaja TIDAK punya stasiun tertentu (prasyarat MB-FORM-15 dan WB-FRM-07), dan satu akun per peran. Menguji di basis data itu membuat banyak langkah "Siapkan…" gugur, dan cakupannya tidak berkurang sedikit pun.</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
@@ -1013,9 +1013,9 @@
           <t>Isinya Tingkat 1 dan 2 saja:
   - Tingkat 1 (170 jalan) setiap kasus SEKALI, pada stasiun wakil. Menyelesaikannya berarti setiap alur sistem sudah pernah dijalankan.
   - Tingkat 2 (95 jalan) lima kasus pada 17 stasiun sisanya: MB-FORM-01, MB-PRV-06, WB-FRM-01, WB-BRW-03, WB-DTL-03, plus LP-W-01. Kelimanya yang gagal kalau satu stasiun salah dikabel.
-YANG TIDAK ADA DI SINI: Tingkat 3 — 1.244 jalan pengulangan penuh per stasiun. Berkas ini TIDAK membuktikan ke-18 stasiun berperilaku benar pada setiap cabang. Ke-18 stasiun punya service, Form, dan Data Preview-nya sendiri-sendiri, jadi bug di satu stasiun tidak mengatakan apa pun tentang yang lain; ketiga defek yang ditemukan pada 2026-10-08 semuanya hanya ada di SATU stasiun.
+YANG TIDAK ADA DI SINI: Tingkat 3 — 1.244 jalan pengulangan penuh per stasiun. Berkas ini TIDAK membuktikan ke-18 stasiun berperilaku benar pada setiap cabang. Ke-18 stasiun punya service, Form, dan Data Preview-nya sendiri-sendiri, jadi bug di satu stasiun tidak mengatakan apa pun tentang yang lain — dan temuan yang pernah ada memang hanya muncul di satu stasiun, bukan di semuanya.
 Pakai berkas tanpa akhiran untuk putaran rilis, atau saring Tingkat 3 di sana pada stasiun yang baru berubah. Kedua berkas dibangun dari skrip yang sama, jadi yang ini tidak dapat tertinggal usang.
-LEBIH DULU DARI MEMANGKAS: jalankan e2e-web/scripts/prepare-db.sh. BrowserTestFixtureSeeder sudah menyiapkan mill, Production Line dengan stasiun aktif setiap jenis, "PL Tanpa &lt;Station&gt;" per keluarga, dan akun keempat peran — banyak langkah "Siapkan..." langsung gugur tanpa mengurangi cakupan sedikit pun.</t>
+LEBIH DULU DARI MEMANGKAS: minta tim pengembang menyiapkan satu basis data uji berisi data contoh (dua mill, stasiun aktif setiap jenis, satu akun per peran). Menguji di sana membuat banyak langkah "Siapkan..." gugur tanpa mengurangi cakupan sedikit pun.</t>
         </is>
       </c>
       <c r="C33" s="6" t="n"/>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="M222" s="14" t="inlineStr">
         <is>
-          <t>angkanya dummy, tetapi hubungan antar angkanya tetap harus benar. Ketiga panel ini dulu ditulis tangan di tiga tempat dan pernah berselisih; sejak 2026-09-30 ketiganya diturunkan dari satu sumber. Yang diuji di sini adalah bahwa ketiganya tidak berselisih lagi.</t>
+          <t>angkanya contoh, tetapi hubungan antar angkanya tetap harus benar. Panel tabel dan grafik menyajikan jam yang sama, jadi keduanya tidak boleh berselisih — dan Total Downtime serta Available Milling Hours harus cocok dengan hitungan manual dari kolomnya sendiri.</t>
         </is>
       </c>
       <c r="N222" s="17" t="n"/>
@@ -17589,7 +17589,7 @@
           <t>- Ditolak dengan pesan validasi yang menunjuk kolom induk.
 - TIDAK ADA galat teknis: bukan stack trace, bukan "SQLSTATE", bukan "Server Error", bukan halaman 500.
 - Pesannya berbahasa Indonesia dan menyebut kolom induknya.
-- Pernah ada bug di sini yang memunculkan galat teknis — perhatikan bentuk pesannya, bukan hanya bahwa ia ditolak.</t>
+- Perhatikan bentuk pesannya, bukan hanya bahwa ia ditolak: pesan validasi di sebelah kolom induk berarti lulus, galat teknis berarti gagal.</t>
         </is>
       </c>
       <c r="L235" s="16" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="M235" s="14" t="inlineStr">
         <is>
-          <t>pernah ada bug di sini yang memunculkan galat teknis, bukan pesan validasi. Perhatikan bentuk pesannya.</t>
+          <t>yang diperiksa bukan hanya bahwa ia ditolak, tetapi bentuk penolakannya. Pesan validasi di sebelah kolom induk berarti lulus; galat teknis berarti gagal, meskipun datanya sama-sama tidak tersimpan.</t>
         </is>
       </c>
       <c r="N235" s="17" t="n"/>
@@ -22287,7 +22287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22298,7 +22298,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Baca ini sebelum melapor</t>
+          <t>Catatan &amp; Batasan — baca sebelum melapor</t>
         </is>
       </c>
     </row>
@@ -22312,14 +22312,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Catatan yang sudah diketahui tim pengembang</t>
+          <t>Batasan yang sudah diketahui</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="40" t="inlineStr">
         <is>
-          <t>Kalau QA menemukannya, cukup rujuk nomornya alih-alih membuat laporan bug baru.</t>
+          <t>Hal-hal di bawah sudah diketahui dan bukan temuan baru. Kalau penguji menemukannya, cukup rujuk nomornya alih-alih membuat laporan bug baru.</t>
         </is>
       </c>
     </row>
@@ -22336,267 +22336,233 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Mengapa begitu</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="27" customHeight="1">
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="83.19999999999999" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>K-1</t>
+          <t>B-1</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>Satuan suhu ditulis C, bukan °C pada laporan Kernel Plant (web &amp; mobile)</t>
+          <t>Laporan periode belum tersedia untuk 7 stasiun</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Disengaja: nilainya datang dari data master apa adanya, dan mengubahnya di tampilan akan membuat web dan mobile berselisih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="94.5" customHeight="1">
+          <t>Engine Room, Process Water, Solid Waste Disposal, Kernel Dispatch, CPO Dispatch, Process Quality Control, dan Effluent Plant belum punya layar laporan periode. Tile-nya tetap TAMPIL di layar Laporan Stasiun dalam keadaan kelabu dan tidak dapat ditekan — supaya pembaca tahu stasiun itu ada. Input data untuk ketujuh stasiun tersebut SUDAH tersedia, baik di web maupun mobile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56.8" customHeight="1">
       <c r="A8" s="41" t="inlineStr">
         <is>
-          <t>K-2</t>
+          <t>B-2</t>
         </is>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>SELESAI 2026-10-08 — penamaan Shell Bin Kernel Loss pada Kernel Plant sudah seragam</t>
+          <t>Layar "Data Saya" belum tersedia</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>Kolom yang dulu bernama shell_loss_percent kini "Shell Bin Kernel Loss" di Form, Detail, Data Preview, Laporan, dan header ekspor CSV — mengikuti nama standar di master. Nama lamanya menyebut zat yang salah: kehilangan SHELL, padahal yang diukur KERNEL yang terbuang ke shell bin. Angkanya tidak pernah salah dan tidak berubah, hanya namanya. Yang diperiksa QA: label barunya konsisten di kelima tempat itu, dan header CSV berbunyi "Shell Bin Kernel Loss (%)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="94.5" customHeight="1">
+          <t>Daftar record yang dibuat pengguna itu sendiri belum ada. Akibatnya akses web untuk peran Station Operator terbatas pada dua layar: Beranda Operator dan Ganti Password. Operator tetap dapat menginput lewat aplikasi mobile seperti biasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96.39999999999999" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>K-3</t>
+          <t>B-3</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>SELESAI 2026-10-08 — jumlah kolom bacaan pada laporan Depricarping sudah benar</t>
+          <t>Dashboard adalah tampilan contoh, bukan laporan mill</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Dulu berbunyi "minimal satu dari ENAM kolom bacaan diisi"; kolom bacaan Depricarping ada SEMBILAN, dan layar yang sama menyebut "sembilan" di tempat lain. Salah di WEB DAN MOBILE (catatan ini dulu menyebut mobile saja), dan bukan kosmetik: angka itu dipakai pembaca untuk menafsirkan penyebut cakupan. Asal-usulnya salin-tempel dari Threshing dan Pressing, yang memang enam kolom. Kini dijaga uji yang menurunkan angkanya dari READING_FIELDS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="27" customHeight="1">
+          <t>Halaman Dashboard menampilkan contoh laporan harian dengan angka tetap — tanpa filter tanggal dan tanpa pemilih mill, dan tidak membaca data stasiun. Ia MENYATAKAN dirinya contoh lewat judul "CPO Mill Demo" dan penanda "Data dummy". Kasus DS-01 justru memeriksa bahwa penanda itu ada; penanda yang hilang adalah temuan prioritas tinggi. Angka operasional yang sebenarnya ada di Laporan Periode per stasiun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="43.59999999999999" customHeight="1">
       <c r="A10" s="41" t="inlineStr">
         <is>
-          <t>K-4</t>
+          <t>B-4</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
+          <t>Satuan suhu ditulis "C", bukan "°C"</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Pada laporan Kernel Plant, web maupun mobile. Disengaja: satuannya mengikuti data master apa adanya, dan mengubahnya di tampilan akan membuat web dan mobile berselisih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30.4" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>B-5</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
           <t>Laporan Depricarping (Mobile): tiga angka pada blok downtime tampil tanpa gaya</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Kosmetik, sudah tercatat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="108" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>K-5</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>DIPERBAIKI 2026-10-08 — catatan ini dulu salah</t>
-        </is>
-      </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Ia berbunyi "Dashboard hanya meringkas 3 stasiun, bukan 18 — disengaja". Blok tiga-stasiun itu SUDAH DIBUANG pada 2026-09-17 atas permintaan user. Keadaan sebenarnya: halaman /dashboard adalah TAMPILAN DEMO dengan angka hard-coded — tanpa filter tanggal, tanpa pemilih mill, tidak membaca data stasiun sama sekali. Ia menyatakan dirinya demo (judul "CPO Mill Demo" + chip "Data dummy"). Ringkasan tiga stasiun kini hanya ada di balik API /api/dashboard/summary, bukan di layar. DS-01..DS-03 ditulis ulang mengikuti keadaan ini.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="41" t="inlineStr">
-        <is>
-          <t>K-6</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>Satu kasus uji otomatis kadang gagal acak (DashboardServiceTest)</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>Tidak memengaruhi perilaku aplikasi; sedang diselidiki.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>K-7</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Cakupan baris kode belum diukur</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada hubungannya dengan hasil pengujian manual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+          <t>Angkanya benar; hanya tampilannya yang belum rapi. Kosmetik, sudah tercatat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Hal yang TERLIHAT seperti bug tetapi BUKAN</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Kasus</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Kelihatan salah</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Sebenarnya</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>LS-16</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Laporan tidak menandai nilai yang jelas di luar batas</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>DISENGAJA. Kolom targetnya teks bebas yang bentuknya tidak dibatasi, dan satu sel bisa memuat dua angka dengan satuan berbeda. Ada kalimat di layar yang menjelaskannya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>MB-FORM-04</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Slot waktu 01:00 dianggap SESUDAH 23:00</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>BENAR. Shift dimulai 07:00, jadi urutannya 07:00 → 23:00 → 00:00 → 06:00.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40.5" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>LS-16</t>
+          <t>DS-02</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Laporan tidak menandai nilai yang jelas di luar batas</t>
+          <t>Dashboard menampilkan angka yang sama untuk semua peran dan semua mill</t>
         </is>
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>DISENGAJA. Kolom targetnya teks bebas yang bentuknya tidak dibatasi, dan satu sel bisa memuat dua angka dengan satuan berbeda. Ada kalimat di layar yang menjelaskannya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="27" customHeight="1">
+          <t>BENAR. Halaman itu tampilan contoh dengan angka tetap, dan menyatakannya lewat penanda "Data dummy". Jangan jalankan uji isolasi mill di sana — ia tidak membaca mill sama sekali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40.5" customHeight="1">
       <c r="A19" s="41" t="inlineStr">
         <is>
-          <t>MB-FORM-04</t>
+          <t>DS-10</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>Slot waktu 01:00 dianggap SESUDAH 23:00</t>
+          <t>Satu stasiun menunjukkan "belum ada input hari ini" DAN "input terakhir 3 menit lalu"</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>BENAR. Shift dimulai 07:00, jadi urutannya 07:00 → 23:00 → 00:00 → 06:00.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40.5" customHeight="1">
+          <t>BENAR. Dua jendela waktu yang berbeda: "hari ini" dibatasi tanggal, "input terakhir" tidak. Keterangan di halaman menjelaskannya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>DS-02</t>
+          <t>LP-W-05</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Dashboard menampilkan angka yang sama untuk semua peran dan semua mill</t>
+          <t>Persen cakupan 0,0% di satu periode dan tanda pisah di periode lain, keduanya "tanpa data"</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>BENAR. Halaman itu demo dengan angka hard-coded, dan menyatakannya lewat chip "Data dummy". Jangan jalankan uji isolasi mill di sana — ia tidak membaca mill sama sekali.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40.5" customHeight="1">
+          <t>BENAR, DAN KEDUANYA BERBEDA. 0,0% = penyebutnya ada, nol yang terisi. Tanda pisah = penyebutnya tidak terbentuk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="41" t="inlineStr">
         <is>
-          <t>DS-10</t>
+          <t>LP-W-03</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>Satu stasiun menunjukkan "belum ada input hari ini" DAN "input terakhir 3 menit lalu"</t>
+          <t>Jumlah slot terisi pada cakupan LEBIH BESAR daripada penyebut parameter mana pun</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>BENAR. Dua jendela waktu yang berbeda: "hari ini" dibatasi tanggal, "input terakhir" tidak. Keterangan di halaman menjelaskannya.</t>
+          <t>BENAR. Slot yang hanya mengisi kolom temuan terhitung terisi tanpa menambah penyebut parameter.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>LP-W-05</t>
+          <t>LS-08</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Persen cakupan 0,0% di satu periode dan tanda pisah di periode lain, keduanya "tanpa data"</t>
+          <t>Production Line tunggal tetap harus dipilih manual</t>
         </is>
       </c>
       <c r="C22" s="28" t="inlineStr">
-        <is>
-          <t>BENAR, DAN KEDUANYA BERBEDA. 0,0% = penyebutnya ada, nol yang terisi. Tanda pisah = penyebutnya tidak terbentuk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="41" t="inlineStr">
-        <is>
-          <t>LP-W-03</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>Jumlah slot terisi pada cakupan LEBIH BESAR daripada penyebut parameter mana pun</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>BENAR. Slot yang hanya mengisi kolom temuan terhitung terisi tanpa menambah penyebut parameter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>LS-08</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Production Line tunggal tetap harus dipilih manual</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>DISENGAJA. Memilihnya otomatis membuat pembaca mengira ia melihat seluruh mill.</t>
         </is>
@@ -22606,9 +22572,9 @@
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
@@ -16677,7 +16677,7 @@
       <c r="Q222" s="17" t="n"/>
       <c r="R222" s="17" t="n"/>
     </row>
-    <row r="223" ht="149.2" customHeight="1">
+    <row r="223" ht="228.4" customHeight="1">
       <c r="A223" s="11" t="n">
         <v>219</v>
       </c>
@@ -16722,15 +16722,18 @@
       <c r="J223" s="14" t="inlineStr">
         <is>
           <t>1. Login di web (buka /login, isi username dan password akun pada kolom Peran, tekan Login) sebagai SPV-A, lalu sidebar → Laporan Stasiun (/reports).
-2. Hitung jumlah tile stasiun di layar.
-3. Hitung berapa tile yang dapat ditekan dan berapa yang kelabu.
-4. Coba tekan satu tile kelabu.
-5. Cari legenda yang menjelaskan arti tile kelabu.</t>
+2. Sebelum memilih apa pun, baca layarnya: catat apakah grid tile stasiun sudah terlihat.
+3. Pada Langkah 1 — Mill &amp; Production Line, pilih salah satu Production Line. (Mill sudah mengikuti akun SPV-A; bila Anda masuk sebagai ADM, pilih mill lebih dulu.)
+4. Hitung jumlah tile stasiun di layar.
+5. Hitung berapa tile yang dapat ditekan dan berapa yang kelabu.
+6. Coba tekan satu tile kelabu.
+7. Cari legenda yang menjelaskan arti tile kelabu.</t>
         </is>
       </c>
       <c r="K223" s="14" t="inlineStr">
         <is>
-          <t>- Seluruh 18 tile tampil — tidak ada yang disembunyikan.
+          <t>- Sebelum Production Line dipilih, grid tile belum muncul — layar menampilkan "Production Line belum dipilih". Ini pola yang sama dengan LS-08: tile membawa konteks mill + line ke layar laporannya, jadi tile ditahan sampai keduanya pasti.
+- Sesudah dipilih, seluruh 18 tile tampil — tidak ada yang disembunyikan.
 - 11 tile aktif dan dapat ditekan; 7 kelabu dan tidak dapat ditekan.
 - Tujuh yang kelabu: Effluent Plant, Engine Room, Process Water, Solid Waste Disposal, Kernel Dispatch, CPO Dispatch, Process Quality Control.
 - Menekan tile kelabu tidak berpindah layar dan tidak memunculkan galat.
@@ -16753,7 +16756,7 @@
       <c r="Q223" s="17" t="n"/>
       <c r="R223" s="17" t="n"/>
     </row>
-    <row r="224" ht="109.6" customHeight="1">
+    <row r="224" ht="136" customHeight="1">
       <c r="A224" s="11" t="n">
         <v>220</v>
       </c>
@@ -16797,7 +16800,7 @@
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>1. Sidebar → Laporan Stasiun sebagai SPV-A.
+          <t>1. Sidebar → Laporan Stasiun sebagai SPV-A, lalu pilih satu Production Line agar grid tile muncul (lihat DS-04).
 2. Tekan tile Pressing. Catat judul layar dan alamatnya.
 3. Periksa apakah mill dan Production Line ikut terbawa (sudah terpilih atau tinggal dipilih).
 4. Tekan Back, lalu ulangi untuk Kernel Plant dan Storage Tank.</t>
@@ -16822,7 +16825,7 @@
       <c r="Q224" s="17" t="n"/>
       <c r="R224" s="17" t="n"/>
     </row>
-    <row r="225" ht="109.6" customHeight="1">
+    <row r="225" ht="162.4" customHeight="1">
       <c r="A225" s="11" t="n">
         <v>221</v>
       </c>
@@ -16851,7 +16854,7 @@
       </c>
       <c r="G225" s="15" t="inlineStr">
         <is>
-          <t>Laporan Manajemen hanya untuk Mill Management dan Admin</t>
+          <t>Laporan Manajemen hanya untuk Mill Management</t>
         </is>
       </c>
       <c r="H225" s="14" t="inlineStr">
@@ -16876,7 +16879,8 @@
         <is>
           <t>- SPV-A: menu tidak ada di sidebar, dan alamat langsung menjawab 403.
 - MGR-A: menu ada dan layarnya terbuka.
-- ADM: menu ada dan layarnya terbuka.</t>
+- ADM: menu tidak ada, dan alamat langsung menjawab 403. Layar ini satu-satunya layar laporan yang lebih sempit dari Dashboard: Admin boleh membuka Dashboard tetapi tidak Laporan Manajemen, karena isinya ditujukan bagi pengelola satu mill, bukan pengelola sistem.
+- Sidebar dan alamat langsung selalu sejalan — tidak ada peran yang melihat menunya lalu ditolak saat menekannya, dan sebaliknya.</t>
         </is>
       </c>
       <c r="L225" s="16" t="inlineStr">

--- a/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -256,6 +256,12 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -272,9 +278,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -678,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -967,48 +970,62 @@
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="7" t="n"/>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Terhalang</t>
+          <t>Tidak berlaku</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Kasus lain yang gagal membuat kasus ini tidak bisa dijalankan. Sebut ID penghalangnya.</t>
+          <t>Kasusnya tidak punya apa pun untuk diuji pada varian itu — kolom Langkah baris itu sudah berbunyi demikian. BUKAN pekerjaan yang tertinggal, jadi tidak ikut dihitung sebagai sisa. Beda dari "Tidak diuji".</t>
         </is>
       </c>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="7" t="n"/>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Terhalang</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Kasus lain yang gagal membuat kasus ini tidak bisa dijalankan. Sebut ID penghalangnya.</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="7" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Sebelum menutup satu putaran</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Periksa tiga hal</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>1) Setiap kasus Prioritas Tinggi punya Hasil, bukan sel kosong. 2) Setiap baris Gagal punya No. Bug. 3) Setiap baris Tidak diuji menyebut prasyarat mana yang tak bisa disiapkan.</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="7" t="n"/>
-    </row>
-    <row r="33" ht="215" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="7" t="n"/>
+    </row>
+    <row r="34" ht="215" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>BERKAS ALUR — 265 JALAN, BUKAN CAKUPAN PENUH</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Isinya Tingkat 1 dan 2 saja:
   - Tingkat 1 (170 jalan) setiap kasus SEKALI, pada stasiun wakil. Menyelesaikannya berarti setiap alur sistem sudah pernah dijalankan.
@@ -1018,43 +1035,44 @@
 LEBIH DULU DARI MEMANGKAS: minta tim pengembang menyiapkan satu basis data uji berisi data contoh (dua mill, stasiun aktif setiap jenis, satu akun per peran). Menguji di sana membuat banyak langkah "Siapkan..." gugur tanpa mengurangi cakupan sedikit pun.</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="7" t="n"/>
-    </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="7" t="n"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Kasus yang prasyaratnya tidak tersedia BUKAN kasus yang lulus. Menandainya Lulus membuat laporan pengujian menyatakan sesuatu yang tidak pernah diperiksa — dan itu lebih berbahaya daripada kolom yang dibiarkan kosong.</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="A35:D35"/>
+  <mergeCells count="29">
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
@@ -1414,7 +1432,7 @@
       <c r="Q7" s="17" t="n"/>
       <c r="R7" s="17" t="n"/>
     </row>
-    <row r="8" ht="175.6" customHeight="1">
+    <row r="8" ht="268" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
@@ -1458,17 +1476,18 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>1. Login di web (buka /login, isi username dan password akun pada kolom Peran, tekan Login) sebagai NOMILL (akun Supervisor yang kolom mill-nya kosong).
-2. Login di web, lalu sidebar &gt; Data &gt; &lt;Stasiun&gt; (/data/&lt;stasiun&gt;) untuk satu stasiun. Baca isi layar.
-3. Login di web, sidebar &gt; Laporan Stasiun (/reports), tekan tile &lt;Stasiun&gt; (/reports/&lt;stasiun&gt;), lalu pilih Periode dan Production Line untuk satu stasiun. Baca isi layar.
-4. Login di web, lalu sidebar &gt; Dashboard (/dashboard). Baca isi layar.</t>
+          <t>1. Buka /login. Isi username dan password NOMILL (akun Supervisor yang kolom mill-nya kosong), tekan Login.
+2. Baca pesan yang muncul kata per kata.
+3. Bila ternyata berhasil masuk, lanjutkan: Login di web, lalu sidebar &gt; Data &gt; &lt;Stasiun&gt; (/data/&lt;stasiun&gt;) satu stasiun, Login di web, sidebar &gt; Laporan Stasiun (/reports), tekan tile &lt;Stasiun&gt; (/reports/&lt;stasiun&gt;), lalu pilih Periode dan Production Line satu stasiun, lalu Login di web, lalu sidebar &gt; Dashboard (/dashboard). Baca isi ketiga layar.</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>- Ketiga layar menampilkan pesan yang menyebut mill — misalnya "Akun Anda belum terhubung ke mill" — atau kalimat sepadan yang menyebut mill.
-- BUKAN tabel kosong. BUKAN angka nol. BUKAN daftar seluruh mill.
-- Pesannya mengarahkan tindakan (mis. menghubungi Admin), bukan sekadar menyatakan tidak ada data.</t>
+          <t>- Akun itu ditolak, bukan dibiarkan masuk lalu melihat layar kosong. Boleh ditolak di Login (tidak pernah sampai ke layar mana pun), boleh juga masuk lalu setiap layar menampilkan pesannya — keduanya sama-sama benar, selama penolakannya disebutkan sebabnya.
+- Pesannya menyebut mill — misalnya "Akun Anda belum terhubung ke mill" — atau kalimat sepadan yang menyebut mill.
+- Pesannya mengarahkan tindakan (mis. menghubungi Admin), bukan sekadar menyatakan ada yang tidak sesuai.
+- Pesannya tidak menyebut pilihan yang tidak pernah dibuat pengguna. Layar Login hanya meminta username dan password; pesan yang menyebut sesuatu "yang dipilih" mengirim pengguna mencari pilihan yang tidak ada.
+- BUKAN tabel kosong. BUKAN angka nol. BUKAN daftar seluruh mill. BUKAN pesan periksa koneksi.</t>
         </is>
       </c>
       <c r="L8" s="16" t="inlineStr">
@@ -1478,7 +1497,7 @@
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>tabel kosong di sini adalah bug, bukan hasil yang benar. Tabel kosong terbaca "mill ini tidak punya data", padahal yang benar "akun Anda belum diatur".</t>
+          <t>tabel kosong di sini adalah bug, bukan hasil yang benar. Tabel kosong terbaca "mill ini tidak punya data", padahal yang benar "akun Anda belum diatur". Hal yang sama berlaku untuk pesan yang benar menolak tetapi salah menyebut sebabnya.</t>
         </is>
       </c>
       <c r="N8" s="17" t="n"/>
@@ -2330,7 +2349,7 @@
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>ketiadaan penandaan di sini disengaja, bukan fitur yang belum selesai. Yang harus dilaporkan sebagai bug adalah kalau penandaan itu muncul, atau kalau kalimat penjelasnya hilang. ---</t>
+          <t>ketiadaan penandaan di sini disengaja, bukan fitur yang belum selesai. Yang harus dilaporkan sebagai bug adalah kalau penandaan itu muncul, atau kalau kalimat penjelasnya hilang.</t>
         </is>
       </c>
       <c r="N20" s="17" t="n"/>
@@ -2955,9 +2974,9 @@
 - Langkah 4 juga diarahkan ke Login.</t>
         </is>
       </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>Tinggi ---</t>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr"/>
@@ -3774,7 +3793,7 @@
       </c>
       <c r="I41" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J41" s="22" t="inlineStr">
@@ -3847,7 +3866,7 @@
       </c>
       <c r="I42" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J42" s="22" t="inlineStr">
@@ -3920,7 +3939,7 @@
       </c>
       <c r="I43" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J43" s="22" t="inlineStr">
@@ -3993,7 +4012,7 @@
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J44" s="22" t="inlineStr">
@@ -4066,7 +4085,7 @@
       </c>
       <c r="I45" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J45" s="22" t="inlineStr">
@@ -4139,7 +4158,7 @@
       </c>
       <c r="I46" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J46" s="22" t="inlineStr">
@@ -4212,7 +4231,7 @@
       </c>
       <c r="I47" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J47" s="22" t="inlineStr">
@@ -4285,7 +4304,7 @@
       </c>
       <c r="I48" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J48" s="22" t="inlineStr">
@@ -4358,7 +4377,7 @@
       </c>
       <c r="I49" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J49" s="22" t="inlineStr">
@@ -4431,7 +4450,7 @@
       </c>
       <c r="I50" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J50" s="22" t="inlineStr">
@@ -4504,7 +4523,7 @@
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
@@ -4577,7 +4596,7 @@
       </c>
       <c r="I52" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J52" s="22" t="inlineStr">
@@ -4650,7 +4669,7 @@
       </c>
       <c r="I53" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J53" s="22" t="inlineStr">
@@ -4723,7 +4742,7 @@
       </c>
       <c r="I54" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J54" s="22" t="inlineStr">
@@ -4796,7 +4815,7 @@
       </c>
       <c r="I55" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J55" s="22" t="inlineStr">
@@ -4869,7 +4888,7 @@
       </c>
       <c r="I56" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J56" s="22" t="inlineStr">
@@ -4942,7 +4961,7 @@
       </c>
       <c r="I57" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J57" s="22" t="inlineStr">
@@ -5015,7 +5034,7 @@
       </c>
       <c r="I58" s="22" t="inlineStr">
         <is>
-          <t>periode stasiun itu Terbuka; Production Line terpilih</t>
+          <t>Prasyarat tambahan untuk Grading: daftar WB Card No pada Form Grading dibaca dari record Weighbridge yang ada di perangkat itu. Pada perangkat yang baru (atau sesudah data aplikasi dibersihkan) daftarnya kosong dan layar berbunyi "Tidak ada data weighbridge lokal", sehingga Grading tidak dapat disimpan. Buat satu record Weighbridge lebih dulu di perangkat yang sama, baru jalankan kasus ini untuk Grading. Itu bukan bug — satu muatan Grading memang menunjuk kartu timbang tertentu. — periode stasiun itu Terbuka; Production Line terpilih</t>
         </is>
       </c>
       <c r="J58" s="22" t="inlineStr">
@@ -5195,7 +5214,7 @@
       <c r="Q60" s="17" t="n"/>
       <c r="R60" s="17" t="n"/>
     </row>
-    <row r="61" ht="136" customHeight="1">
+    <row r="61" ht="386.8" customHeight="1">
       <c r="A61" s="11" t="n">
         <v>57</v>
       </c>
@@ -5239,7 +5258,7 @@
       </c>
       <c r="J61" s="14" t="inlineStr">
         <is>
-          <t>1. Login di mobile, buka Monitor Depricarping, lalu tekan New Data (/stations/depricarping/form/&lt;id&gt;) (lewati untuk keempat stasiun per-transaksi).
+          <t>1. Login di mobile, buka Monitor Depricarping, lalu tekan New Data (/stations/depricarping/form/&lt;id&gt;) (lewati ketujuh stasiun di luar daftar itu).
 2. Tambah satu baris slot waktu. Buka pemilih slotnya.
 3. Catat urutan lengkap pilihan dari atas ke bawah.
 4. Bandingkan dengan urutan yang benar: 07:00, 08:00, …, 23:00, 00:00, 01:00, …, 06:00.</t>
@@ -5261,7 +5280,8 @@
       </c>
       <c r="M61" s="14" t="inlineStr">
         <is>
-          <t>ini kasus yang paling mudah salah dibaca sebagai bug padahal benar, dan sebaliknya. Shift dimulai 07:00.</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".
+ini kasus yang paling mudah salah dibaca sebagai bug padahal benar, dan sebaliknya. Shift dimulai 07:00.</t>
         </is>
       </c>
       <c r="N61" s="17" t="n"/>
@@ -5832,7 +5852,7 @@
       <c r="Q69" s="17" t="n"/>
       <c r="R69" s="17" t="n"/>
     </row>
-    <row r="70" ht="136" customHeight="1">
+    <row r="70" ht="294.4" customHeight="1">
       <c r="A70" s="11" t="n">
         <v>66</v>
       </c>
@@ -5876,11 +5896,9 @@
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>1. Buat satu record sebagai OPR-A, simpan.
-2. Login di mobile, buka Monitor Depricarping, lalu tekan New Data (/stations/depricarping/form/&lt;id&gt;) sebagai SPV-A, buka record itu. Isi Checked By, tekan Simpan.
-3. Periksa kolom Acknowledged By sebagai SPV-A.
-4. Logout. Buka record yang sama sebagai MGR-A. Isi Acknowledged By, tekan Simpan.
-5. Periksa kolom Checked By sebagai MGR-A.</t>
+          <t>1. Login di mobile, buka Monitor Depricarping, lalu tekan New Data (/stations/depricarping/form/&lt;id&gt;) sebagai SPV-A. Isi satu record. Periksa kolom Checked By dan
+Acknowledged By sebelum menyimpan, lalu Simpan.
+2. Logout. Login di mobile, buka Monitor Depricarping, lalu tekan New Data (/stations/depricarping/form/&lt;id&gt;) sebagai MGR-A. Ulangi langkah 1 dan periksa kedua kolom yang sama.</t>
         </is>
       </c>
       <c r="K70" s="14" t="inlineStr">
@@ -5889,7 +5907,9 @@
 - SPV-A tidak dapat mengisi Acknowledged By.
 - MGR-A dapat mengisi Acknowledged By.
 - MGR-A tidak dapat mengisi Checked By.
-- Nama yang terisi adalah nama pengguna yang mengisinya, bukan diketik bebas.</t>
+- Nama yang terisi adalah nama pengguna yang mengisinya, bukan diketik bebas — kendalinya kotak
+centang, bukan kolom teks.
+- Kendali yang tidak boleh dipakai sebaiknya tidak ditampilkan sama sekali untuk peran itu.</t>
         </is>
       </c>
       <c r="L70" s="16" t="inlineStr">
@@ -5897,7 +5917,11 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M70" s="14" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr">
+        <is>
+          <t>Catatan jalan: di aplikasi mobile, daftar Data Preview dibaca dari basis data di perangkat itu dan milik pengguna yang sedang masuk. Record yang dibuat OPR-A tidak terlihat oleh SPV-A meski di perangkat yang sama, dan belum ada alur sinkronisasi yang menarik record pengguna lain ke perangkat. Jadi "buka record OPR-A sebagai SPV-A" tidak dapat dijalankan di mobile — itu batas alur yang ada, bukan bug. Verifikasi atas record orang lain diuji di web (WB-FRM-08). Yang diuji di sini adalah aturan perannya di mobile, pada record yang dibuat peran itu sendiri.</t>
+        </is>
+      </c>
       <c r="N70" s="17" t="n"/>
       <c r="O70" s="17" t="n"/>
       <c r="P70" s="17" t="n"/>
@@ -8122,7 +8146,7 @@
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>Rendah ---</t>
+          <t>Rendah</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr"/>
@@ -8272,7 +8296,7 @@
       <c r="Q104" s="17" t="n"/>
       <c r="R104" s="17" t="n"/>
     </row>
-    <row r="105" ht="136" customHeight="1">
+    <row r="105" ht="334" customHeight="1">
       <c r="A105" s="18" t="n">
         <v>101</v>
       </c>
@@ -8314,15 +8338,287 @@
           <t>satu record dengan 3 baris terisi</t>
         </is>
       </c>
-      <c r="J105" s="22" t="inlineStr">
+      <c r="J105" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="K105" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="L105" s="18" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="M105" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
+        </is>
+      </c>
+      <c r="N105" s="24" t="n"/>
+      <c r="O105" s="24" t="n"/>
+      <c r="P105" s="24" t="n"/>
+      <c r="Q105" s="24" t="n"/>
+      <c r="R105" s="24" t="n"/>
+    </row>
+    <row r="106" ht="334" customHeight="1">
+      <c r="A106" s="18" t="n">
+        <v>102</v>
+      </c>
+      <c r="B106" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03 / Grading</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03</t>
+        </is>
+      </c>
+      <c r="E106" s="21" t="inlineStr">
+        <is>
+          <t>Grading</t>
+        </is>
+      </c>
+      <c r="F106" s="22" t="inlineStr">
+        <is>
+          <t>Web — Data Stasiun (WB-)</t>
+        </is>
+      </c>
+      <c r="G106" s="21" t="inlineStr">
+        <is>
+          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>SPV-A</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>satu record dengan 3 baris terisi</t>
+        </is>
+      </c>
+      <c r="J106" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="K106" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="L106" s="18" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="M106" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
+        </is>
+      </c>
+      <c r="N106" s="24" t="n"/>
+      <c r="O106" s="24" t="n"/>
+      <c r="P106" s="24" t="n"/>
+      <c r="Q106" s="24" t="n"/>
+      <c r="R106" s="24" t="n"/>
+    </row>
+    <row r="107" ht="334" customHeight="1">
+      <c r="A107" s="18" t="n">
+        <v>103</v>
+      </c>
+      <c r="B107" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03 / Cages Track</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03</t>
+        </is>
+      </c>
+      <c r="E107" s="21" t="inlineStr">
+        <is>
+          <t>Cages Track</t>
+        </is>
+      </c>
+      <c r="F107" s="22" t="inlineStr">
+        <is>
+          <t>Web — Data Stasiun (WB-)</t>
+        </is>
+      </c>
+      <c r="G107" s="21" t="inlineStr">
+        <is>
+          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
+        </is>
+      </c>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>SPV-A</t>
+        </is>
+      </c>
+      <c r="I107" s="22" t="inlineStr">
+        <is>
+          <t>satu record dengan 3 baris terisi</t>
+        </is>
+      </c>
+      <c r="J107" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="K107" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="L107" s="18" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="M107" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
+        </is>
+      </c>
+      <c r="N107" s="24" t="n"/>
+      <c r="O107" s="24" t="n"/>
+      <c r="P107" s="24" t="n"/>
+      <c r="Q107" s="24" t="n"/>
+      <c r="R107" s="24" t="n"/>
+    </row>
+    <row r="108" ht="334" customHeight="1">
+      <c r="A108" s="18" t="n">
+        <v>104</v>
+      </c>
+      <c r="B108" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03 / Sterilizer</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03</t>
+        </is>
+      </c>
+      <c r="E108" s="21" t="inlineStr">
+        <is>
+          <t>Sterilizer</t>
+        </is>
+      </c>
+      <c r="F108" s="22" t="inlineStr">
+        <is>
+          <t>Web — Data Stasiun (WB-)</t>
+        </is>
+      </c>
+      <c r="G108" s="21" t="inlineStr">
+        <is>
+          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
+        </is>
+      </c>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t>SPV-A</t>
+        </is>
+      </c>
+      <c r="I108" s="22" t="inlineStr">
+        <is>
+          <t>satu record dengan 3 baris terisi</t>
+        </is>
+      </c>
+      <c r="J108" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="K108" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="L108" s="18" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="M108" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
+        </is>
+      </c>
+      <c r="N108" s="24" t="n"/>
+      <c r="O108" s="24" t="n"/>
+      <c r="P108" s="24" t="n"/>
+      <c r="Q108" s="24" t="n"/>
+      <c r="R108" s="24" t="n"/>
+    </row>
+    <row r="109" ht="334" customHeight="1">
+      <c r="A109" s="18" t="n">
+        <v>105</v>
+      </c>
+      <c r="B109" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03 / Threshing</t>
+        </is>
+      </c>
+      <c r="D109" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03</t>
+        </is>
+      </c>
+      <c r="E109" s="21" t="inlineStr">
+        <is>
+          <t>Threshing</t>
+        </is>
+      </c>
+      <c r="F109" s="22" t="inlineStr">
+        <is>
+          <t>Web — Data Stasiun (WB-)</t>
+        </is>
+      </c>
+      <c r="G109" s="21" t="inlineStr">
+        <is>
+          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
+        </is>
+      </c>
+      <c r="H109" s="22" t="inlineStr">
+        <is>
+          <t>SPV-A</t>
+        </is>
+      </c>
+      <c r="I109" s="22" t="inlineStr">
+        <is>
+          <t>satu record dengan 3 baris terisi</t>
+        </is>
+      </c>
+      <c r="J109" s="22" t="inlineStr">
         <is>
           <t>1. Siapkan satu record dengan tepat 3 baris slot waktu terisi.
-2. Login di web, lalu sidebar &gt; Data &gt; Weighbridge (/data/weighbridge), cari record itu.
+2. Login di web, lalu sidebar &gt; Data &gt; Threshing (/data/threshing), cari record itu.
 3. Baca kolom Jumlah Baris Terisi pada baris itu.
 4. Bandingkan dengan jumlah baris sebenarnya pada Detail record tersebut.</t>
         </is>
       </c>
-      <c r="K105" s="22" t="inlineStr">
+      <c r="K109" s="22" t="inlineStr">
         <is>
           <t>- Tertulis sebagai pecahan dari 24 — mis. 3 / 24 atau 3 dari 24.
 - Angka pertamanya 3, cocok dengan Detail.
@@ -8330,310 +8626,14 @@
 - Untuk stasiun per-transaksi (Weighbridge, Grading, Kernel Dispatch, CPO Dispatch), kolom ini boleh berbeda bentuknya — catat apa adanya.</t>
         </is>
       </c>
-      <c r="L105" s="18" t="inlineStr">
+      <c r="L109" s="18" t="inlineStr">
         <is>
           <t>Sedang</t>
         </is>
       </c>
-      <c r="M105" s="22" t="inlineStr">
-        <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
-        </is>
-      </c>
-      <c r="N105" s="17" t="n"/>
-      <c r="O105" s="17" t="n"/>
-      <c r="P105" s="17" t="n"/>
-      <c r="Q105" s="17" t="n"/>
-      <c r="R105" s="17" t="n"/>
-    </row>
-    <row r="106" ht="136" customHeight="1">
-      <c r="A106" s="18" t="n">
-        <v>102</v>
-      </c>
-      <c r="B106" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C106" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03 / Grading</t>
-        </is>
-      </c>
-      <c r="D106" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03</t>
-        </is>
-      </c>
-      <c r="E106" s="21" t="inlineStr">
-        <is>
-          <t>Grading</t>
-        </is>
-      </c>
-      <c r="F106" s="22" t="inlineStr">
-        <is>
-          <t>Web — Data Stasiun (WB-)</t>
-        </is>
-      </c>
-      <c r="G106" s="21" t="inlineStr">
-        <is>
-          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
-        </is>
-      </c>
-      <c r="H106" s="22" t="inlineStr">
-        <is>
-          <t>SPV-A</t>
-        </is>
-      </c>
-      <c r="I106" s="22" t="inlineStr">
-        <is>
-          <t>satu record dengan 3 baris terisi</t>
-        </is>
-      </c>
-      <c r="J106" s="22" t="inlineStr">
-        <is>
-          <t>1. Siapkan satu record dengan tepat 3 baris slot waktu terisi.
-2. Login di web, lalu sidebar &gt; Data &gt; Grading (/data/grading), cari record itu.
-3. Baca kolom Jumlah Baris Terisi pada baris itu.
-4. Bandingkan dengan jumlah baris sebenarnya pada Detail record tersebut.</t>
-        </is>
-      </c>
-      <c r="K106" s="22" t="inlineStr">
-        <is>
-          <t>- Tertulis sebagai pecahan dari 24 — mis. 3 / 24 atau 3 dari 24.
-- Angka pertamanya 3, cocok dengan Detail.
-- BUKAN hanya 3 tanpa penyebut: tanpa penyebut pembaca tidak tahu seberapa lengkap recordnya.
-- Untuk stasiun per-transaksi (Weighbridge, Grading, Kernel Dispatch, CPO Dispatch), kolom ini boleh berbeda bentuknya — catat apa adanya.</t>
-        </is>
-      </c>
-      <c r="L106" s="18" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="M106" s="22" t="inlineStr">
-        <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
-        </is>
-      </c>
-      <c r="N106" s="17" t="n"/>
-      <c r="O106" s="17" t="n"/>
-      <c r="P106" s="17" t="n"/>
-      <c r="Q106" s="17" t="n"/>
-      <c r="R106" s="17" t="n"/>
-    </row>
-    <row r="107" ht="136" customHeight="1">
-      <c r="A107" s="18" t="n">
-        <v>103</v>
-      </c>
-      <c r="B107" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C107" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03 / Cages Track</t>
-        </is>
-      </c>
-      <c r="D107" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03</t>
-        </is>
-      </c>
-      <c r="E107" s="21" t="inlineStr">
-        <is>
-          <t>Cages Track</t>
-        </is>
-      </c>
-      <c r="F107" s="22" t="inlineStr">
-        <is>
-          <t>Web — Data Stasiun (WB-)</t>
-        </is>
-      </c>
-      <c r="G107" s="21" t="inlineStr">
-        <is>
-          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
-        </is>
-      </c>
-      <c r="H107" s="22" t="inlineStr">
-        <is>
-          <t>SPV-A</t>
-        </is>
-      </c>
-      <c r="I107" s="22" t="inlineStr">
-        <is>
-          <t>satu record dengan 3 baris terisi</t>
-        </is>
-      </c>
-      <c r="J107" s="22" t="inlineStr">
-        <is>
-          <t>1. Siapkan satu record dengan tepat 3 baris slot waktu terisi.
-2. Login di web, lalu sidebar &gt; Data &gt; Cages Track (/data/cages-track), cari record itu.
-3. Baca kolom Jumlah Baris Terisi pada baris itu.
-4. Bandingkan dengan jumlah baris sebenarnya pada Detail record tersebut.</t>
-        </is>
-      </c>
-      <c r="K107" s="22" t="inlineStr">
-        <is>
-          <t>- Tertulis sebagai pecahan dari 24 — mis. 3 / 24 atau 3 dari 24.
-- Angka pertamanya 3, cocok dengan Detail.
-- BUKAN hanya 3 tanpa penyebut: tanpa penyebut pembaca tidak tahu seberapa lengkap recordnya.
-- Untuk stasiun per-transaksi (Weighbridge, Grading, Kernel Dispatch, CPO Dispatch), kolom ini boleh berbeda bentuknya — catat apa adanya.</t>
-        </is>
-      </c>
-      <c r="L107" s="18" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="M107" s="22" t="inlineStr">
-        <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
-        </is>
-      </c>
-      <c r="N107" s="17" t="n"/>
-      <c r="O107" s="17" t="n"/>
-      <c r="P107" s="17" t="n"/>
-      <c r="Q107" s="17" t="n"/>
-      <c r="R107" s="17" t="n"/>
-    </row>
-    <row r="108" ht="136" customHeight="1">
-      <c r="A108" s="18" t="n">
-        <v>104</v>
-      </c>
-      <c r="B108" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C108" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03 / Sterilizer</t>
-        </is>
-      </c>
-      <c r="D108" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03</t>
-        </is>
-      </c>
-      <c r="E108" s="21" t="inlineStr">
-        <is>
-          <t>Sterilizer</t>
-        </is>
-      </c>
-      <c r="F108" s="22" t="inlineStr">
-        <is>
-          <t>Web — Data Stasiun (WB-)</t>
-        </is>
-      </c>
-      <c r="G108" s="21" t="inlineStr">
-        <is>
-          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
-        </is>
-      </c>
-      <c r="H108" s="22" t="inlineStr">
-        <is>
-          <t>SPV-A</t>
-        </is>
-      </c>
-      <c r="I108" s="22" t="inlineStr">
-        <is>
-          <t>satu record dengan 3 baris terisi</t>
-        </is>
-      </c>
-      <c r="J108" s="22" t="inlineStr">
-        <is>
-          <t>1. Siapkan satu record dengan tepat 3 baris slot waktu terisi.
-2. Login di web, lalu sidebar &gt; Data &gt; Sterilizer (/data/sterilizer), cari record itu.
-3. Baca kolom Jumlah Baris Terisi pada baris itu.
-4. Bandingkan dengan jumlah baris sebenarnya pada Detail record tersebut.</t>
-        </is>
-      </c>
-      <c r="K108" s="22" t="inlineStr">
-        <is>
-          <t>- Tertulis sebagai pecahan dari 24 — mis. 3 / 24 atau 3 dari 24.
-- Angka pertamanya 3, cocok dengan Detail.
-- BUKAN hanya 3 tanpa penyebut: tanpa penyebut pembaca tidak tahu seberapa lengkap recordnya.
-- Untuk stasiun per-transaksi (Weighbridge, Grading, Kernel Dispatch, CPO Dispatch), kolom ini boleh berbeda bentuknya — catat apa adanya.</t>
-        </is>
-      </c>
-      <c r="L108" s="18" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="M108" s="22" t="inlineStr">
-        <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
-        </is>
-      </c>
-      <c r="N108" s="17" t="n"/>
-      <c r="O108" s="17" t="n"/>
-      <c r="P108" s="17" t="n"/>
-      <c r="Q108" s="17" t="n"/>
-      <c r="R108" s="17" t="n"/>
-    </row>
-    <row r="109" ht="136" customHeight="1">
-      <c r="A109" s="18" t="n">
-        <v>105</v>
-      </c>
-      <c r="B109" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C109" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03 / Threshing</t>
-        </is>
-      </c>
-      <c r="D109" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03</t>
-        </is>
-      </c>
-      <c r="E109" s="21" t="inlineStr">
-        <is>
-          <t>Threshing</t>
-        </is>
-      </c>
-      <c r="F109" s="22" t="inlineStr">
-        <is>
-          <t>Web — Data Stasiun (WB-)</t>
-        </is>
-      </c>
-      <c r="G109" s="21" t="inlineStr">
-        <is>
-          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
-        </is>
-      </c>
-      <c r="H109" s="22" t="inlineStr">
-        <is>
-          <t>SPV-A</t>
-        </is>
-      </c>
-      <c r="I109" s="22" t="inlineStr">
-        <is>
-          <t>satu record dengan 3 baris terisi</t>
-        </is>
-      </c>
-      <c r="J109" s="22" t="inlineStr">
-        <is>
-          <t>1. Siapkan satu record dengan tepat 3 baris slot waktu terisi.
-2. Login di web, lalu sidebar &gt; Data &gt; Threshing (/data/threshing), cari record itu.
-3. Baca kolom Jumlah Baris Terisi pada baris itu.
-4. Bandingkan dengan jumlah baris sebenarnya pada Detail record tersebut.</t>
-        </is>
-      </c>
-      <c r="K109" s="22" t="inlineStr">
-        <is>
-          <t>- Tertulis sebagai pecahan dari 24 — mis. 3 / 24 atau 3 dari 24.
-- Angka pertamanya 3, cocok dengan Detail.
-- BUKAN hanya 3 tanpa penyebut: tanpa penyebut pembaca tidak tahu seberapa lengkap recordnya.
-- Untuk stasiun per-transaksi (Weighbridge, Grading, Kernel Dispatch, CPO Dispatch), kolom ini boleh berbeda bentuknya — catat apa adanya.</t>
-        </is>
-      </c>
-      <c r="L109" s="18" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
       <c r="M109" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N109" s="17" t="n"/>
@@ -8642,7 +8642,7 @@
       <c r="Q109" s="17" t="n"/>
       <c r="R109" s="17" t="n"/>
     </row>
-    <row r="110" ht="136" customHeight="1">
+    <row r="110" ht="334" customHeight="1">
       <c r="A110" s="18" t="n">
         <v>106</v>
       </c>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="M110" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N110" s="17" t="n"/>
@@ -8716,7 +8716,7 @@
       <c r="Q110" s="17" t="n"/>
       <c r="R110" s="17" t="n"/>
     </row>
-    <row r="111" ht="136" customHeight="1">
+    <row r="111" ht="334" customHeight="1">
       <c r="A111" s="18" t="n">
         <v>107</v>
       </c>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="M111" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N111" s="17" t="n"/>
@@ -8790,7 +8790,7 @@
       <c r="Q111" s="17" t="n"/>
       <c r="R111" s="17" t="n"/>
     </row>
-    <row r="112" ht="136" customHeight="1">
+    <row r="112" ht="334" customHeight="1">
       <c r="A112" s="18" t="n">
         <v>108</v>
       </c>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="M112" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N112" s="17" t="n"/>
@@ -8864,7 +8864,7 @@
       <c r="Q112" s="17" t="n"/>
       <c r="R112" s="17" t="n"/>
     </row>
-    <row r="113" ht="136" customHeight="1">
+    <row r="113" ht="334" customHeight="1">
       <c r="A113" s="18" t="n">
         <v>109</v>
       </c>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="M113" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N113" s="17" t="n"/>
@@ -8938,7 +8938,7 @@
       <c r="Q113" s="17" t="n"/>
       <c r="R113" s="17" t="n"/>
     </row>
-    <row r="114" ht="136" customHeight="1">
+    <row r="114" ht="334" customHeight="1">
       <c r="A114" s="18" t="n">
         <v>110</v>
       </c>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="M114" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N114" s="17" t="n"/>
@@ -9012,7 +9012,7 @@
       <c r="Q114" s="17" t="n"/>
       <c r="R114" s="17" t="n"/>
     </row>
-    <row r="115" ht="136" customHeight="1">
+    <row r="115" ht="334" customHeight="1">
       <c r="A115" s="11" t="n">
         <v>111</v>
       </c>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M115" s="14" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N115" s="17" t="n"/>
@@ -9086,7 +9086,7 @@
       <c r="Q115" s="17" t="n"/>
       <c r="R115" s="17" t="n"/>
     </row>
-    <row r="116" ht="136" customHeight="1">
+    <row r="116" ht="334" customHeight="1">
       <c r="A116" s="18" t="n">
         <v>112</v>
       </c>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="M116" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N116" s="17" t="n"/>
@@ -9160,7 +9160,7 @@
       <c r="Q116" s="17" t="n"/>
       <c r="R116" s="17" t="n"/>
     </row>
-    <row r="117" ht="136" customHeight="1">
+    <row r="117" ht="334" customHeight="1">
       <c r="A117" s="18" t="n">
         <v>113</v>
       </c>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="M117" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N117" s="17" t="n"/>
@@ -9234,7 +9234,7 @@
       <c r="Q117" s="17" t="n"/>
       <c r="R117" s="17" t="n"/>
     </row>
-    <row r="118" ht="136" customHeight="1">
+    <row r="118" ht="334" customHeight="1">
       <c r="A118" s="18" t="n">
         <v>114</v>
       </c>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M118" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N118" s="17" t="n"/>
@@ -9308,7 +9308,7 @@
       <c r="Q118" s="17" t="n"/>
       <c r="R118" s="17" t="n"/>
     </row>
-    <row r="119" ht="136" customHeight="1">
+    <row r="119" ht="334" customHeight="1">
       <c r="A119" s="18" t="n">
         <v>115</v>
       </c>
@@ -9350,15 +9350,219 @@
           <t>satu record dengan 3 baris terisi</t>
         </is>
       </c>
-      <c r="J119" s="22" t="inlineStr">
+      <c r="J119" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="K119" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="L119" s="18" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="M119" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
+        </is>
+      </c>
+      <c r="N119" s="24" t="n"/>
+      <c r="O119" s="24" t="n"/>
+      <c r="P119" s="24" t="n"/>
+      <c r="Q119" s="24" t="n"/>
+      <c r="R119" s="24" t="n"/>
+    </row>
+    <row r="120" ht="334" customHeight="1">
+      <c r="A120" s="18" t="n">
+        <v>116</v>
+      </c>
+      <c r="B120" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03 / Kernel Dispatch</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03</t>
+        </is>
+      </c>
+      <c r="E120" s="21" t="inlineStr">
+        <is>
+          <t>Kernel Dispatch</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t>Web — Data Stasiun (WB-)</t>
+        </is>
+      </c>
+      <c r="G120" s="21" t="inlineStr">
+        <is>
+          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
+        <is>
+          <t>SPV-A</t>
+        </is>
+      </c>
+      <c r="I120" s="22" t="inlineStr">
+        <is>
+          <t>satu record dengan 3 baris terisi</t>
+        </is>
+      </c>
+      <c r="J120" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="K120" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="L120" s="18" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="M120" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
+        </is>
+      </c>
+      <c r="N120" s="24" t="n"/>
+      <c r="O120" s="24" t="n"/>
+      <c r="P120" s="24" t="n"/>
+      <c r="Q120" s="24" t="n"/>
+      <c r="R120" s="24" t="n"/>
+    </row>
+    <row r="121" ht="334" customHeight="1">
+      <c r="A121" s="18" t="n">
+        <v>117</v>
+      </c>
+      <c r="B121" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C121" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03 / CPO Dispatch</t>
+        </is>
+      </c>
+      <c r="D121" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03</t>
+        </is>
+      </c>
+      <c r="E121" s="21" t="inlineStr">
+        <is>
+          <t>CPO Dispatch</t>
+        </is>
+      </c>
+      <c r="F121" s="22" t="inlineStr">
+        <is>
+          <t>Web — Data Stasiun (WB-)</t>
+        </is>
+      </c>
+      <c r="G121" s="21" t="inlineStr">
+        <is>
+          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
+        </is>
+      </c>
+      <c r="H121" s="22" t="inlineStr">
+        <is>
+          <t>SPV-A</t>
+        </is>
+      </c>
+      <c r="I121" s="22" t="inlineStr">
+        <is>
+          <t>satu record dengan 3 baris terisi</t>
+        </is>
+      </c>
+      <c r="J121" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="K121" s="23" t="inlineStr">
+        <is>
+          <t>Tidak berlaku — grid stasiun ini bukan 24 slot waktu; ia menghitung satuannya sendiri (siklus / cage-lori / kejadian / nomor kendaraan / satu transaksi per record)</t>
+        </is>
+      </c>
+      <c r="L121" s="18" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="M121" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
+        </is>
+      </c>
+      <c r="N121" s="24" t="n"/>
+      <c r="O121" s="24" t="n"/>
+      <c r="P121" s="24" t="n"/>
+      <c r="Q121" s="24" t="n"/>
+      <c r="R121" s="24" t="n"/>
+    </row>
+    <row r="122" ht="334" customHeight="1">
+      <c r="A122" s="18" t="n">
+        <v>118</v>
+      </c>
+      <c r="B122" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03 / Process Quality Control</t>
+        </is>
+      </c>
+      <c r="D122" s="20" t="inlineStr">
+        <is>
+          <t>WB-BRW-03</t>
+        </is>
+      </c>
+      <c r="E122" s="21" t="inlineStr">
+        <is>
+          <t>Process Quality Control</t>
+        </is>
+      </c>
+      <c r="F122" s="22" t="inlineStr">
+        <is>
+          <t>Web — Data Stasiun (WB-)</t>
+        </is>
+      </c>
+      <c r="G122" s="21" t="inlineStr">
+        <is>
+          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t>SPV-A</t>
+        </is>
+      </c>
+      <c r="I122" s="22" t="inlineStr">
+        <is>
+          <t>satu record dengan 3 baris terisi</t>
+        </is>
+      </c>
+      <c r="J122" s="22" t="inlineStr">
         <is>
           <t>1. Siapkan satu record dengan tepat 3 baris slot waktu terisi.
-2. Login di web, lalu sidebar &gt; Data &gt; Solid Waste Disposal (/data/solid-waste-disposal), cari record itu.
+2. Login di web, lalu sidebar &gt; Data &gt; Process Quality Control (/data/process-quality-control), cari record itu.
 3. Baca kolom Jumlah Baris Terisi pada baris itu.
 4. Bandingkan dengan jumlah baris sebenarnya pada Detail record tersebut.</t>
         </is>
       </c>
-      <c r="K119" s="22" t="inlineStr">
+      <c r="K122" s="22" t="inlineStr">
         <is>
           <t>- Tertulis sebagai pecahan dari 24 — mis. 3 / 24 atau 3 dari 24.
 - Angka pertamanya 3, cocok dengan Detail.
@@ -9366,236 +9570,14 @@
 - Untuk stasiun per-transaksi (Weighbridge, Grading, Kernel Dispatch, CPO Dispatch), kolom ini boleh berbeda bentuknya — catat apa adanya.</t>
         </is>
       </c>
-      <c r="L119" s="18" t="inlineStr">
+      <c r="L122" s="18" t="inlineStr">
         <is>
           <t>Sedang</t>
         </is>
       </c>
-      <c r="M119" s="22" t="inlineStr">
-        <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
-        </is>
-      </c>
-      <c r="N119" s="17" t="n"/>
-      <c r="O119" s="17" t="n"/>
-      <c r="P119" s="17" t="n"/>
-      <c r="Q119" s="17" t="n"/>
-      <c r="R119" s="17" t="n"/>
-    </row>
-    <row r="120" ht="136" customHeight="1">
-      <c r="A120" s="18" t="n">
-        <v>116</v>
-      </c>
-      <c r="B120" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C120" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03 / Kernel Dispatch</t>
-        </is>
-      </c>
-      <c r="D120" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03</t>
-        </is>
-      </c>
-      <c r="E120" s="21" t="inlineStr">
-        <is>
-          <t>Kernel Dispatch</t>
-        </is>
-      </c>
-      <c r="F120" s="22" t="inlineStr">
-        <is>
-          <t>Web — Data Stasiun (WB-)</t>
-        </is>
-      </c>
-      <c r="G120" s="21" t="inlineStr">
-        <is>
-          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
-        </is>
-      </c>
-      <c r="H120" s="22" t="inlineStr">
-        <is>
-          <t>SPV-A</t>
-        </is>
-      </c>
-      <c r="I120" s="22" t="inlineStr">
-        <is>
-          <t>satu record dengan 3 baris terisi</t>
-        </is>
-      </c>
-      <c r="J120" s="22" t="inlineStr">
-        <is>
-          <t>1. Siapkan satu record dengan tepat 3 baris slot waktu terisi.
-2. Login di web, lalu sidebar &gt; Data &gt; Kernel Dispatch (/data/kernel-dispatch), cari record itu.
-3. Baca kolom Jumlah Baris Terisi pada baris itu.
-4. Bandingkan dengan jumlah baris sebenarnya pada Detail record tersebut.</t>
-        </is>
-      </c>
-      <c r="K120" s="22" t="inlineStr">
-        <is>
-          <t>- Tertulis sebagai pecahan dari 24 — mis. 3 / 24 atau 3 dari 24.
-- Angka pertamanya 3, cocok dengan Detail.
-- BUKAN hanya 3 tanpa penyebut: tanpa penyebut pembaca tidak tahu seberapa lengkap recordnya.
-- Untuk stasiun per-transaksi (Weighbridge, Grading, Kernel Dispatch, CPO Dispatch), kolom ini boleh berbeda bentuknya — catat apa adanya.</t>
-        </is>
-      </c>
-      <c r="L120" s="18" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="M120" s="22" t="inlineStr">
-        <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
-        </is>
-      </c>
-      <c r="N120" s="17" t="n"/>
-      <c r="O120" s="17" t="n"/>
-      <c r="P120" s="17" t="n"/>
-      <c r="Q120" s="17" t="n"/>
-      <c r="R120" s="17" t="n"/>
-    </row>
-    <row r="121" ht="136" customHeight="1">
-      <c r="A121" s="18" t="n">
-        <v>117</v>
-      </c>
-      <c r="B121" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C121" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03 / CPO Dispatch</t>
-        </is>
-      </c>
-      <c r="D121" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03</t>
-        </is>
-      </c>
-      <c r="E121" s="21" t="inlineStr">
-        <is>
-          <t>CPO Dispatch</t>
-        </is>
-      </c>
-      <c r="F121" s="22" t="inlineStr">
-        <is>
-          <t>Web — Data Stasiun (WB-)</t>
-        </is>
-      </c>
-      <c r="G121" s="21" t="inlineStr">
-        <is>
-          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
-        </is>
-      </c>
-      <c r="H121" s="22" t="inlineStr">
-        <is>
-          <t>SPV-A</t>
-        </is>
-      </c>
-      <c r="I121" s="22" t="inlineStr">
-        <is>
-          <t>satu record dengan 3 baris terisi</t>
-        </is>
-      </c>
-      <c r="J121" s="22" t="inlineStr">
-        <is>
-          <t>1. Siapkan satu record dengan tepat 3 baris slot waktu terisi.
-2. Login di web, lalu sidebar &gt; Data &gt; CPO Dispatch (/data/cpo-dispatch), cari record itu.
-3. Baca kolom Jumlah Baris Terisi pada baris itu.
-4. Bandingkan dengan jumlah baris sebenarnya pada Detail record tersebut.</t>
-        </is>
-      </c>
-      <c r="K121" s="22" t="inlineStr">
-        <is>
-          <t>- Tertulis sebagai pecahan dari 24 — mis. 3 / 24 atau 3 dari 24.
-- Angka pertamanya 3, cocok dengan Detail.
-- BUKAN hanya 3 tanpa penyebut: tanpa penyebut pembaca tidak tahu seberapa lengkap recordnya.
-- Untuk stasiun per-transaksi (Weighbridge, Grading, Kernel Dispatch, CPO Dispatch), kolom ini boleh berbeda bentuknya — catat apa adanya.</t>
-        </is>
-      </c>
-      <c r="L121" s="18" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="M121" s="22" t="inlineStr">
-        <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
-        </is>
-      </c>
-      <c r="N121" s="17" t="n"/>
-      <c r="O121" s="17" t="n"/>
-      <c r="P121" s="17" t="n"/>
-      <c r="Q121" s="17" t="n"/>
-      <c r="R121" s="17" t="n"/>
-    </row>
-    <row r="122" ht="136" customHeight="1">
-      <c r="A122" s="18" t="n">
-        <v>118</v>
-      </c>
-      <c r="B122" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C122" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03 / Process Quality Control</t>
-        </is>
-      </c>
-      <c r="D122" s="20" t="inlineStr">
-        <is>
-          <t>WB-BRW-03</t>
-        </is>
-      </c>
-      <c r="E122" s="21" t="inlineStr">
-        <is>
-          <t>Process Quality Control</t>
-        </is>
-      </c>
-      <c r="F122" s="22" t="inlineStr">
-        <is>
-          <t>Web — Data Stasiun (WB-)</t>
-        </is>
-      </c>
-      <c r="G122" s="21" t="inlineStr">
-        <is>
-          <t>"Jumlah Baris Terisi" tampil sebagai pecahan dari 24</t>
-        </is>
-      </c>
-      <c r="H122" s="22" t="inlineStr">
-        <is>
-          <t>SPV-A</t>
-        </is>
-      </c>
-      <c r="I122" s="22" t="inlineStr">
-        <is>
-          <t>satu record dengan 3 baris terisi</t>
-        </is>
-      </c>
-      <c r="J122" s="22" t="inlineStr">
-        <is>
-          <t>1. Siapkan satu record dengan tepat 3 baris slot waktu terisi.
-2. Login di web, lalu sidebar &gt; Data &gt; Process Quality Control (/data/process-quality-control), cari record itu.
-3. Baca kolom Jumlah Baris Terisi pada baris itu.
-4. Bandingkan dengan jumlah baris sebenarnya pada Detail record tersebut.</t>
-        </is>
-      </c>
-      <c r="K122" s="22" t="inlineStr">
-        <is>
-          <t>- Tertulis sebagai pecahan dari 24 — mis. 3 / 24 atau 3 dari 24.
-- Angka pertamanya 3, cocok dengan Detail.
-- BUKAN hanya 3 tanpa penyebut: tanpa penyebut pembaca tidak tahu seberapa lengkap recordnya.
-- Untuk stasiun per-transaksi (Weighbridge, Grading, Kernel Dispatch, CPO Dispatch), kolom ini boleh berbeda bentuknya — catat apa adanya.</t>
-        </is>
-      </c>
-      <c r="L122" s="18" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
       <c r="M122" s="22" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N122" s="17" t="n"/>
@@ -10156,7 +10138,7 @@
       <c r="Q130" s="17" t="n"/>
       <c r="R130" s="17" t="n"/>
     </row>
-    <row r="131" ht="109.6" customHeight="1">
+    <row r="131" ht="254.8" customHeight="1">
       <c r="A131" s="18" t="n">
         <v>127</v>
       </c>
@@ -10218,14 +10200,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M131" s="22" t="inlineStr"/>
+      <c r="M131" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N131" s="17" t="n"/>
       <c r="O131" s="17" t="n"/>
       <c r="P131" s="17" t="n"/>
       <c r="Q131" s="17" t="n"/>
       <c r="R131" s="17" t="n"/>
     </row>
-    <row r="132" ht="109.6" customHeight="1">
+    <row r="132" ht="254.8" customHeight="1">
       <c r="A132" s="18" t="n">
         <v>128</v>
       </c>
@@ -10287,14 +10273,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M132" s="22" t="inlineStr"/>
+      <c r="M132" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N132" s="17" t="n"/>
       <c r="O132" s="17" t="n"/>
       <c r="P132" s="17" t="n"/>
       <c r="Q132" s="17" t="n"/>
       <c r="R132" s="17" t="n"/>
     </row>
-    <row r="133" ht="109.6" customHeight="1">
+    <row r="133" ht="254.8" customHeight="1">
       <c r="A133" s="18" t="n">
         <v>129</v>
       </c>
@@ -10356,14 +10346,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M133" s="22" t="inlineStr"/>
+      <c r="M133" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N133" s="17" t="n"/>
       <c r="O133" s="17" t="n"/>
       <c r="P133" s="17" t="n"/>
       <c r="Q133" s="17" t="n"/>
       <c r="R133" s="17" t="n"/>
     </row>
-    <row r="134" ht="109.6" customHeight="1">
+    <row r="134" ht="254.8" customHeight="1">
       <c r="A134" s="18" t="n">
         <v>130</v>
       </c>
@@ -10425,14 +10419,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M134" s="22" t="inlineStr"/>
+      <c r="M134" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N134" s="17" t="n"/>
       <c r="O134" s="17" t="n"/>
       <c r="P134" s="17" t="n"/>
       <c r="Q134" s="17" t="n"/>
       <c r="R134" s="17" t="n"/>
     </row>
-    <row r="135" ht="109.6" customHeight="1">
+    <row r="135" ht="254.8" customHeight="1">
       <c r="A135" s="18" t="n">
         <v>131</v>
       </c>
@@ -10494,14 +10492,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M135" s="22" t="inlineStr"/>
+      <c r="M135" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N135" s="17" t="n"/>
       <c r="O135" s="17" t="n"/>
       <c r="P135" s="17" t="n"/>
       <c r="Q135" s="17" t="n"/>
       <c r="R135" s="17" t="n"/>
     </row>
-    <row r="136" ht="109.6" customHeight="1">
+    <row r="136" ht="254.8" customHeight="1">
       <c r="A136" s="18" t="n">
         <v>132</v>
       </c>
@@ -10563,14 +10565,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M136" s="22" t="inlineStr"/>
+      <c r="M136" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N136" s="17" t="n"/>
       <c r="O136" s="17" t="n"/>
       <c r="P136" s="17" t="n"/>
       <c r="Q136" s="17" t="n"/>
       <c r="R136" s="17" t="n"/>
     </row>
-    <row r="137" ht="109.6" customHeight="1">
+    <row r="137" ht="254.8" customHeight="1">
       <c r="A137" s="18" t="n">
         <v>133</v>
       </c>
@@ -10632,14 +10638,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M137" s="22" t="inlineStr"/>
+      <c r="M137" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N137" s="17" t="n"/>
       <c r="O137" s="17" t="n"/>
       <c r="P137" s="17" t="n"/>
       <c r="Q137" s="17" t="n"/>
       <c r="R137" s="17" t="n"/>
     </row>
-    <row r="138" ht="109.6" customHeight="1">
+    <row r="138" ht="254.8" customHeight="1">
       <c r="A138" s="18" t="n">
         <v>134</v>
       </c>
@@ -10701,14 +10711,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M138" s="22" t="inlineStr"/>
+      <c r="M138" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N138" s="17" t="n"/>
       <c r="O138" s="17" t="n"/>
       <c r="P138" s="17" t="n"/>
       <c r="Q138" s="17" t="n"/>
       <c r="R138" s="17" t="n"/>
     </row>
-    <row r="139" ht="109.6" customHeight="1">
+    <row r="139" ht="254.8" customHeight="1">
       <c r="A139" s="18" t="n">
         <v>135</v>
       </c>
@@ -10770,14 +10784,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M139" s="22" t="inlineStr"/>
+      <c r="M139" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N139" s="17" t="n"/>
       <c r="O139" s="17" t="n"/>
       <c r="P139" s="17" t="n"/>
       <c r="Q139" s="17" t="n"/>
       <c r="R139" s="17" t="n"/>
     </row>
-    <row r="140" ht="109.6" customHeight="1">
+    <row r="140" ht="254.8" customHeight="1">
       <c r="A140" s="18" t="n">
         <v>136</v>
       </c>
@@ -10839,14 +10857,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M140" s="22" t="inlineStr"/>
+      <c r="M140" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N140" s="17" t="n"/>
       <c r="O140" s="17" t="n"/>
       <c r="P140" s="17" t="n"/>
       <c r="Q140" s="17" t="n"/>
       <c r="R140" s="17" t="n"/>
     </row>
-    <row r="141" ht="109.6" customHeight="1">
+    <row r="141" ht="254.8" customHeight="1">
       <c r="A141" s="11" t="n">
         <v>137</v>
       </c>
@@ -10908,14 +10930,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M141" s="14" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N141" s="17" t="n"/>
       <c r="O141" s="17" t="n"/>
       <c r="P141" s="17" t="n"/>
       <c r="Q141" s="17" t="n"/>
       <c r="R141" s="17" t="n"/>
     </row>
-    <row r="142" ht="109.6" customHeight="1">
+    <row r="142" ht="254.8" customHeight="1">
       <c r="A142" s="18" t="n">
         <v>138</v>
       </c>
@@ -10977,14 +11003,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M142" s="22" t="inlineStr"/>
+      <c r="M142" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N142" s="17" t="n"/>
       <c r="O142" s="17" t="n"/>
       <c r="P142" s="17" t="n"/>
       <c r="Q142" s="17" t="n"/>
       <c r="R142" s="17" t="n"/>
     </row>
-    <row r="143" ht="109.6" customHeight="1">
+    <row r="143" ht="254.8" customHeight="1">
       <c r="A143" s="18" t="n">
         <v>139</v>
       </c>
@@ -11046,14 +11076,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M143" s="22" t="inlineStr"/>
+      <c r="M143" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N143" s="17" t="n"/>
       <c r="O143" s="17" t="n"/>
       <c r="P143" s="17" t="n"/>
       <c r="Q143" s="17" t="n"/>
       <c r="R143" s="17" t="n"/>
     </row>
-    <row r="144" ht="109.6" customHeight="1">
+    <row r="144" ht="254.8" customHeight="1">
       <c r="A144" s="18" t="n">
         <v>140</v>
       </c>
@@ -11115,14 +11149,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M144" s="22" t="inlineStr"/>
+      <c r="M144" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N144" s="17" t="n"/>
       <c r="O144" s="17" t="n"/>
       <c r="P144" s="17" t="n"/>
       <c r="Q144" s="17" t="n"/>
       <c r="R144" s="17" t="n"/>
     </row>
-    <row r="145" ht="109.6" customHeight="1">
+    <row r="145" ht="254.8" customHeight="1">
       <c r="A145" s="18" t="n">
         <v>141</v>
       </c>
@@ -11184,14 +11222,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M145" s="22" t="inlineStr"/>
+      <c r="M145" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N145" s="17" t="n"/>
       <c r="O145" s="17" t="n"/>
       <c r="P145" s="17" t="n"/>
       <c r="Q145" s="17" t="n"/>
       <c r="R145" s="17" t="n"/>
     </row>
-    <row r="146" ht="109.6" customHeight="1">
+    <row r="146" ht="254.8" customHeight="1">
       <c r="A146" s="18" t="n">
         <v>142</v>
       </c>
@@ -11253,14 +11295,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M146" s="22" t="inlineStr"/>
+      <c r="M146" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N146" s="17" t="n"/>
       <c r="O146" s="17" t="n"/>
       <c r="P146" s="17" t="n"/>
       <c r="Q146" s="17" t="n"/>
       <c r="R146" s="17" t="n"/>
     </row>
-    <row r="147" ht="109.6" customHeight="1">
+    <row r="147" ht="254.8" customHeight="1">
       <c r="A147" s="18" t="n">
         <v>143</v>
       </c>
@@ -11322,14 +11368,18 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M147" s="22" t="inlineStr"/>
+      <c r="M147" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N147" s="17" t="n"/>
       <c r="O147" s="17" t="n"/>
       <c r="P147" s="17" t="n"/>
       <c r="Q147" s="17" t="n"/>
       <c r="R147" s="17" t="n"/>
     </row>
-    <row r="148" ht="109.6" customHeight="1">
+    <row r="148" ht="254.8" customHeight="1">
       <c r="A148" s="18" t="n">
         <v>144</v>
       </c>
@@ -11391,7 +11441,11 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M148" s="22" t="inlineStr"/>
+      <c r="M148" s="22" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: seluruh stasiun, tetapi penyebut 24 hanya untuk 11 stasiun bergrid slot waktu (lihat daftarnya di WB-BRW-03). Pada tujuh stasiun lain, bandingkan jumlah baris grid dengan jumlah yang tertulis di kolom hitungannya sendiri — "Jumlah Siklus", "Jumlah Cage/Lori Tercatat", atau "Jumlah Kejadian" — bukan dengan 24. Sebuah record yang memang punya 24 baris terisi harus menampilkan 24 baris; yang dilarang adalah menggambar 24 baris ketika yang tersimpan lebih sedikit.</t>
+        </is>
+      </c>
       <c r="N148" s="17" t="n"/>
       <c r="O148" s="17" t="n"/>
       <c r="P148" s="17" t="n"/>
@@ -12885,7 +12939,7 @@
       <c r="Q169" s="17" t="n"/>
       <c r="R169" s="17" t="n"/>
     </row>
-    <row r="170" ht="162.4" customHeight="1">
+    <row r="170" ht="215.2" customHeight="1">
       <c r="A170" s="11" t="n">
         <v>166</v>
       </c>
@@ -12933,7 +12987,8 @@
 2. Kosongkan kolom identitas unit, isi yang lain dengan benar, tekan Simpan. Catat letak pesannya.
 3. Isi identitas, lalu kosongkan Tanggal, tekan Simpan.
 4. Isi Tanggal dengan teks yang bukan tanggal (mis. abc), tekan Simpan.
-5. Isi Tanggal dengan tanggal di luar periode yang terbuka, tekan Simpan.</t>
+5. Isi Tanggal dengan tanggal di luar periode yang terbuka — pilih tanggal di masa lalu
+(mis. dua bulan sebelum periode dimulai), tekan Simpan.</t>
         </is>
       </c>
       <c r="K170" s="14" t="inlineStr">
@@ -12941,6 +12996,9 @@
           <t>- Setiap langkah ditolak; record tidak tersimpan.
 - Setiap pesan galat muncul di sebelah kolom yang bersangkutan.
 - Tanggal di luar periode terbuka ditolak dengan pesan yang menyebut periode.
+- Jangan memakai tanggal masa depan untuk langkah 5: tanggal masa depan ditolak lebih dulu
+oleh aturan tersendiri ("tidak boleh melewati hari ini"), sehingga pesan periodenya tidak akan
+pernah muncul dan kasus ini tampak gagal padahal menguji hal yang salah.
 - Isi kolom lain tidak hilang setiap kali penolakan terjadi.</t>
         </is>
       </c>
@@ -12956,7 +13014,7 @@
       <c r="Q170" s="17" t="n"/>
       <c r="R170" s="17" t="n"/>
     </row>
-    <row r="171" ht="122.8" customHeight="1">
+    <row r="171" ht="334" customHeight="1">
       <c r="A171" s="11" t="n">
         <v>167</v>
       </c>
@@ -13000,7 +13058,7 @@
       </c>
       <c r="J171" s="14" t="inlineStr">
         <is>
-          <t>1. Login di web, buka /data/depricarping (Depricarping), lalu tekan Tambah (/data/depricarping/create) (lewati untuk keempat stasiun per-transaksi).
+          <t>1. Login di web, buka /data/depricarping (Depricarping), lalu tekan Tambah (/data/depricarping/create) (lewati ketujuh stasiun di luar daftar itu).
 2. Jalankan seluruh langkah MB-FORM-03 pada form web ini: coba slot menurun dan slot kembar.
 3. Jalankan seluruh langkah MB-FORM-04: baca urutan 24 pilihan slot.</t>
         </is>
@@ -13008,7 +13066,14 @@
       <c r="K171" s="14" t="inlineStr">
         <is>
           <t>- Aturan slotnya sama persis dengan mobile: harus menaik, tidak boleh kembar.
-- Urutannya 07:00 → 23:00 → 00:00 → 06:00, tepat 24 pilihan.
+- Urutannya 07:00 → 23:00 → 00:00 → 06:00, tepat 24 pilihan pada baris pertama.
+- Aturannya ditegakkan dengan mencegah, bukan dengan pesan galat: pada baris kedua dan
+seterusnya, daftar pilihan hanya memuat slot yang lebih besar dari slot baris sebelumnya —
+slot yang sudah dipakai dan slot yang lebih awal hilang dari daftar. Jadi Anda tidak akan
+bisa memilih slot kembar atau menurun, dan tidak akan ada pesan galat untuk dibaca. Itu yang
+benar; mencegah lebih kuat daripada menolak saat Simpan.
+- Yang dilaporkan sebagai temuan adalah kebalikannya: bila slot kembar atau menurun ternyata
+masih bisa dipilih.
 - Bila web dan mobile berbeda di titik mana pun, catat perbedaannya — itu temuan.</t>
         </is>
       </c>
@@ -13019,7 +13084,7 @@
       </c>
       <c r="M171" s="14" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N171" s="17" t="n"/>
@@ -13028,7 +13093,7 @@
       <c r="Q171" s="17" t="n"/>
       <c r="R171" s="17" t="n"/>
     </row>
-    <row r="172" ht="109.6" customHeight="1">
+    <row r="172" ht="334" customHeight="1">
       <c r="A172" s="11" t="n">
         <v>168</v>
       </c>
@@ -13072,7 +13137,7 @@
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>1. Login di web, buka /data/depricarping (Depricarping), lalu tekan Tambah (/data/depricarping/create) (lewati untuk keempat stasiun per-transaksi).
+          <t>1. Login di web, buka /data/depricarping (Depricarping), lalu tekan Tambah (/data/depricarping/create) (lewati ketujuh stasiun di luar daftar itu).
 2. Isi header dengan benar.
 3. Tambah baris terus-menerus sampai mencapai 24 baris.
 4. Coba tambah baris ke-25.</t>
@@ -13092,7 +13157,7 @@
       </c>
       <c r="M172" s="14" t="inlineStr">
         <is>
-          <t>lewati untuk 4 stasiun per-transaksi</t>
+          <t>Berlaku untuk: 11 stasiun bergrid 24 slot waktu — Boiler Room, Clarification, Depricarping, Effluent Plant, Engine Room, Kernel Plant, Pressing, Process Quality Control, Process Water, Storage Tank, Threshing. Tujuh stasiun lain menghitung hal yang berbeda dan memang tidak memakai penyebut 24: Sterilizer menghitung siklus, Cages Track menghitung cage/lori, Solid Waste Disposal / Kernel Dispatch / CPO Dispatch menghitung kejadian, Grading menampilkan nomor kendaraan, dan Weighbridge satu record berarti satu transaksi. Pada ketujuh stasiun itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
         </is>
       </c>
       <c r="N172" s="17" t="n"/>
@@ -13238,7 +13303,7 @@
       <c r="Q174" s="17" t="n"/>
       <c r="R174" s="17" t="n"/>
     </row>
-    <row r="175" ht="136" customHeight="1">
+    <row r="175" ht="188.8" customHeight="1">
       <c r="A175" s="11" t="n">
         <v>171</v>
       </c>
@@ -13293,8 +13358,11 @@
         <is>
           <t>- SPV-A: Checked By bisa, Acknowledged By tidak.
 - MGR-A: Acknowledged By bisa, Checked By tidak.
-- ADM: keduanya bisa.
-- Kolom yang tidak boleh diisi disertai keterangan siapa yang berhak (lihat LS-14).</t>
+- ADM: keduanya tidak — verifikasi adalah pernyataan diri, dan Admin bukan pihak yang
+memeriksa maupun mengonfirmasi. Bagi Admin, bagian Verifikasi tidak ditampilkan sama
+sekali. Itu bukan bug.
+- Kendali yang tidak boleh dipakai sebaiknya tidak ditampilkan, bukan ditampilkan kelabu;
+bila ditampilkan kelabu, harus ada keterangan siapa yang berhak (lihat LS-14).</t>
         </is>
       </c>
       <c r="L175" s="16" t="inlineStr">
@@ -14814,7 +14882,7 @@
       <c r="Q196" s="17" t="n"/>
       <c r="R196" s="17" t="n"/>
     </row>
-    <row r="197" ht="162.4" customHeight="1">
+    <row r="197" ht="281.2" customHeight="1">
       <c r="A197" s="11" t="n">
         <v>193</v>
       </c>
@@ -14878,7 +14946,11 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M197" s="14" t="inlineStr"/>
+      <c r="M197" s="14" t="inlineStr">
+        <is>
+          <t>periksa keduanya terpisah. Yang paling berbahaya adalah angka atau nama Production Line mill lama yang tertinggal — itu bug prioritas tinggi. Bila yang terjadi hanya pemilih periode yang langsung mendarat pada satu-satunya periode mill baru (sementara line tetap kosong dan angkanya tetap belum muncul), catat itu apa adanya sebagai selisih dari hasil yang diharapkan: tidak ada data yang bocor, tetapi pembaca mendapat periode yang tidak pernah ia pilih. Sebutkan nama periode yang terpilih sendiri itu dalam laporan Anda.</t>
+        </is>
+      </c>
       <c r="N197" s="17" t="n"/>
       <c r="O197" s="17" t="n"/>
       <c r="P197" s="17" t="n"/>
@@ -16437,9 +16509,9 @@
 - Tidak ada kolom input di layar ini selain pemilih periode/line/mill.</t>
         </is>
       </c>
-      <c r="L219" s="11" t="inlineStr">
-        <is>
-          <t>Tinggi ---</t>
+      <c r="L219" s="16" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
         </is>
       </c>
       <c r="M219" s="14" t="inlineStr"/>
@@ -17320,7 +17392,7 @@
       </c>
       <c r="M231" s="14" t="inlineStr">
         <is>
-          <t>urutan ini bukan alfabetis dan bukan alur proses — ia urutan yang diminta produk. Yang diuji adalah web dan mobile tidak menyimpang satu dari yang lain. ---</t>
+          <t>urutan ini bukan alfabetis dan bukan alur proses — ia urutan yang diminta produk. Yang diuji adalah web dan mobile tidak menyimpang satu dari yang lain.</t>
         </is>
       </c>
       <c r="N231" s="17" t="n"/>
@@ -17468,7 +17540,7 @@
       <c r="Q233" s="17" t="n"/>
       <c r="R233" s="17" t="n"/>
     </row>
-    <row r="234" ht="122.8" customHeight="1">
+    <row r="234" ht="162.4" customHeight="1">
       <c r="A234" s="11" t="n">
         <v>230</v>
       </c>
@@ -17497,32 +17569,34 @@
       </c>
       <c r="G234" s="15" t="inlineStr">
         <is>
-          <t>Nama kembar ditolak, tidak peduli huruf besar-kecil</t>
+          <t>Entri kembar ditolak, tidak peduli huruf besar-kecil</t>
         </is>
       </c>
       <c r="H234" s="14" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>ADM - Kolom yang diperiksa berbeda per tingkat — pakai kolom yang berlaku di tingkat yang sedang diuji, jangan menguji kolom yang memang tidak dibatasi: | Tingkat | Kolom yang tidak boleh kembar | Lingkupnya | |---|---|---| | Corporate | Nama | seluruh sistem | | Company | Nama | di dalam Corporate induknya (lihat MD-KEL-05) | | Business Unit | Kode | seluruh sistem | | Production Line | Kode | seluruh sistem | | Station | Kode | seluruh sistem | | Machinery Group | Kode | seluruh sistem | | Machinery | Kode Equipment | seluruh sistem | | User &amp; Role | Username | seluruh sistem | Di lima tingkat yang dibatasi lewat Kode, nama kembar memang diperbolehkan — dua mill boleh bernama sama selama kodenya berbeda. Itu bukan bug; jangan laporkan.</t>
         </is>
       </c>
       <c r="I234" s="14" t="inlineStr">
         <is>
-          <t>sudah ada entri bernama mis. PT Contoh</t>
+          <t>sudah ada satu entri dengan nilai acuan, mis. kode CONTOH-1</t>
         </is>
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>1. Login di web, lalu sidebar &gt; Kelola Business Unit (/master-data/business-units) sebagai ADM. Buat satu entri bernama PT Contoh.
-2. Tekan Tambah lagi, isi nama pt contoh (huruf kecil), Simpan.
-3. Tekan Tambah lagi, isi nama PT CONTOH (huruf besar), Simpan.
-4. Tekan Tambah lagi, isi   PT Contoh   (dengan spasi di depan dan belakang), Simpan.</t>
+          <t>1. Login di web, lalu sidebar &gt; Kelola Business Unit (/master-data/business-units) sebagai ADM. Buat satu entri dengan nilai acuan pada kolom
+dari tabel di atas (mis. kode CONTOH-1).
+2. Tekan Tambah lagi, isi kolom itu dengan nilai yang sama berhuruf kecil (contoh-1), Simpan.
+3. Tekan Tambah lagi, isi berhuruf besar (CONTOH-1), Simpan.
+4. Tekan Tambah lagi, isi dengan spasi di depan dan belakang (  CONTOH-1  ), Simpan.</t>
         </is>
       </c>
       <c r="K234" s="14" t="inlineStr">
         <is>
-          <t>- Langkah 2, 3, dan 4 semuanya ditolak.
-- Pesannya menyebut bahwa namanya sudah dipakai.
-- Hanya satu entri yang ada di daftar.</t>
+          <t>- Langkah 3 dan 4 ditolak, dengan pesan yang menyebut kolom itu sudah dipakai.
+- Langkah 2 (beda huruf besar-kecil) juga ditolak — kembar yang hanya berbeda kapital akan
+terbaca sebagai dua hal berbeda oleh sistem tetapi satu hal yang sama oleh manusia.
+- Hanya satu entri dengan nilai itu yang ada di daftar.</t>
         </is>
       </c>
       <c r="L234" s="16" t="inlineStr">
@@ -17612,7 +17686,7 @@
       <c r="Q235" s="17" t="n"/>
       <c r="R235" s="17" t="n"/>
     </row>
-    <row r="236" ht="136" customHeight="1">
+    <row r="236" ht="202" customHeight="1">
       <c r="A236" s="11" t="n">
         <v>232</v>
       </c>
@@ -17621,7 +17695,7 @@
       </c>
       <c r="C236" s="13" t="inlineStr">
         <is>
-          <t>MD-KEL-05 / Business Unit</t>
+          <t>MD-KEL-05 / Company</t>
         </is>
       </c>
       <c r="D236" s="13" t="inlineStr">
@@ -17631,7 +17705,7 @@
       </c>
       <c r="E236" s="15" t="inlineStr">
         <is>
-          <t>Business Unit</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="F236" s="14" t="inlineStr">
@@ -17657,7 +17731,7 @@
       <c r="J236" s="14" t="inlineStr">
         <is>
           <t>1. Sebagai ADM, pastikan ada dua Corporate berbeda: Corporate A dan Corporate B.
-2. Login di web, lalu sidebar &gt; Kelola Business Unit (/master-data/business-units) untuk Company. Tambah Company bernama PT Sama dengan induk Corporate A. Simpan.
+2. Login di web, lalu sidebar &gt; Kelola Company (/master-data/companies). Tambah Company bernama PT Sama dengan induk Corporate A. Simpan.
 3. Tambah Company bernama PT Sama dengan induk Corporate B. Simpan.
 4. Tambah Company bernama PT Sama dengan induk Corporate A lagi. Simpan.</t>
         </is>
@@ -17674,7 +17748,11 @@
           <t>Sedang</t>
         </is>
       </c>
-      <c r="M236" s="14" t="inlineStr"/>
+      <c r="M236" s="14" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: hanya Company. Itu satu-satunya tingkat yang namanya dibatasi per induk ("Nama company sudah digunakan pada Corporate ini"). Corporate dibatasi secara global, dan lima tingkat lainnya tidak membatasi nama sama sekali — hanya kodenya, dan kode dibatasi secara global, bukan per induk. Pada tingkat selain Company tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal".</t>
+        </is>
+      </c>
       <c r="N236" s="17" t="n"/>
       <c r="O236" s="17" t="n"/>
       <c r="P236" s="17" t="n"/>
@@ -17958,7 +18036,7 @@
       <c r="Q240" s="17" t="n"/>
       <c r="R240" s="17" t="n"/>
     </row>
-    <row r="241" ht="162.4" customHeight="1">
+    <row r="241" ht="228.4" customHeight="1">
       <c r="A241" s="11" t="n">
         <v>237</v>
       </c>
@@ -17967,7 +18045,7 @@
       </c>
       <c r="C241" s="13" t="inlineStr">
         <is>
-          <t>MD-KEL-10 / Business Unit</t>
+          <t>MD-KEL-10 / Machinery</t>
         </is>
       </c>
       <c r="D241" s="13" t="inlineStr">
@@ -17977,7 +18055,7 @@
       </c>
       <c r="E241" s="15" t="inlineStr">
         <is>
-          <t>Business Unit</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="F241" s="14" t="inlineStr">
@@ -18002,7 +18080,7 @@
       </c>
       <c r="J241" s="14" t="inlineStr">
         <is>
-          <t>1. Login di web, lalu sidebar &gt; Kelola Business Unit (/master-data/business-units) sebagai ADM. Pastikan datanya lebih dari satu halaman.
+          <t>1. Login di web, lalu sidebar &gt; Kelola Machinery (/master-data/machinery) sebagai ADM. Pastikan datanya lebih dari satu halaman.
 2. Ketik satu kata kunci yang hasilnya lebih dari satu halaman.
 3. Catat jumlah total hasil yang tertulis.
 4. Buka halaman 2.
@@ -18022,7 +18100,11 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M241" s="14" t="inlineStr"/>
+      <c r="M241" s="14" t="inlineStr">
+        <is>
+          <t>Berlaku untuk: hanya Kelola Mesin. Dari delapan tingkat Kelola, hanya layar itu yang punya kolom pencarian teks bebas; tujuh lainnya (Corporate, Company, Business Unit, Production Line, Station, Machinery Group, User &amp; Role) menyaring lewat pemilih induk, bukan pencarian. Pada tujuh layar itu kasus ini tidak berlaku — tandai "Tidak berlaku" dengan sebab itu, jangan "Gagal". Pencarian mill diuji terpisah di MD-STR-04.</t>
+        </is>
+      </c>
       <c r="N241" s="17" t="n"/>
       <c r="O241" s="17" t="n"/>
       <c r="P241" s="17" t="n"/>
@@ -18038,7 +18120,7 @@
       </c>
       <c r="C242" s="13" t="inlineStr">
         <is>
-          <t>MD-KEL-11 / Business Unit</t>
+          <t>MD-KEL-11 / Machinery</t>
         </is>
       </c>
       <c r="D242" s="13" t="inlineStr">
@@ -18048,7 +18130,7 @@
       </c>
       <c r="E242" s="15" t="inlineStr">
         <is>
-          <t>Business Unit</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="F242" s="14" t="inlineStr">
@@ -18073,7 +18155,7 @@
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>1. Login di web, lalu sidebar &gt; Kelola Business Unit (/master-data/business-units) sebagai ADM. Buat dua entri: Mill 100% Murni dan Mill BU_A. Bila memungkinkan, buat juga Mill BUxA.
+          <t>1. Login di web, lalu sidebar &gt; Kelola Machinery (/master-data/machinery) sebagai ADM. Buat dua entri: Mill 100% Murni dan Mill BU_A. Bila memungkinkan, buat juga Mill BUxA.
 2. Cari 100%. Catat hasilnya.
 3. Hapus, cari BU_A. Catat hasilnya.
 4. Hapus, cari mill (huruf kecil). Catat hasilnya.</t>
@@ -18094,7 +18176,8 @@
       </c>
       <c r="M242" s="14" t="inlineStr">
         <is>
-          <t>% dan _ adalah karakter khusus pencarian di banyak sistem. Di sini keduanya harus diperlakukan sebagai huruf biasa.</t>
+          <t>Berlaku untuk: hanya Kelola Mesin, dengan sebab yang sama seperti MD-KEL-10.
+% dan _ adalah karakter khusus pencarian di banyak sistem. Di sini keduanya harus diperlakukan sebagai huruf biasa.</t>
         </is>
       </c>
       <c r="N242" s="17" t="n"/>
@@ -19275,7 +19358,7 @@
       </c>
       <c r="L259" s="11" t="inlineStr">
         <is>
-          <t>Sedang ---</t>
+          <t>Sedang</t>
         </is>
       </c>
       <c r="M259" s="14" t="inlineStr"/>
@@ -19703,7 +19786,7 @@
       <c r="Q265" s="17" t="n"/>
       <c r="R265" s="17" t="n"/>
     </row>
-    <row r="266" ht="96.39999999999999" customHeight="1">
+    <row r="266" ht="175.6" customHeight="1">
       <c r="A266" s="11" t="n">
         <v>262</v>
       </c>
@@ -19765,7 +19848,11 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="M266" s="14" t="inlineStr"/>
+      <c r="M266" s="14" t="inlineStr">
+        <is>
+          <t>layar ini tidak menyebut nama mill yang sedang diatur untuk peran Mill Management — isinya berbunyi "untuk mill Anda". Itu bukan bagian dari hasil yang diuji di atas, jadi jangan dilaporkan sebagai bug; catat saja bila menurut Anda perlu ditegaskan. Untuk Admin, mill yang sedang diatur selalu terlihat karena ada pemilihnya (AD-08).</t>
+        </is>
+      </c>
       <c r="N266" s="17" t="n"/>
       <c r="O266" s="17" t="n"/>
       <c r="P266" s="17" t="n"/>
@@ -19908,7 +19995,7 @@
       <c r="Q268" s="17" t="n"/>
       <c r="R268" s="17" t="n"/>
     </row>
-    <row r="269" ht="149.2" customHeight="1">
+    <row r="269" ht="294.4" customHeight="1">
       <c r="A269" s="11" t="n">
         <v>265</v>
       </c>
@@ -19942,7 +20029,7 @@
       </c>
       <c r="H269" s="14" t="inlineStr">
         <is>
-          <t>MGR-A</t>
+          <t>MGR-A (web) + OPR-A (mobile)</t>
         </is>
       </c>
       <c r="I269" s="14" t="inlineStr">
@@ -19952,28 +20039,34 @@
       </c>
       <c r="J269" s="14" t="inlineStr">
         <is>
-          <t>1. Login di web, lalu sidebar &gt; Mills Setting (/mill-settings) sebagai MGR-A. Catat nilai awal salah satu pengaturan.
+          <t>1. Login di web, lalu sidebar &gt; Mills Setting (/mill-settings) sebagai MGR-A. Catat nilai awal Nama Aplikasi.
 2. Ubah nilai itu, tekan Simpan.
 3. Muat ulang halaman (F5). Baca nilainya.
-4. Buka layar yang memakai pengaturan itu (mis. Form Cages Track untuk pengaturan Jumlah Cages).
-5. Periksa apakah nilai baru benar-benar berpengaruh di sana.
-6. Kembalikan nilainya ke semula.</t>
+4. Login di mobile (buka aplikasi, isi username dan password, tekan Login), mendarat di /home sebagai OPR-A pada mill yang sama, lalu sinkronkan bila diminta.
+5. Baca nama aplikasi yang tampil di layar Home mobile.
+6. Kembalikan nilainya ke semula lewat Login di web, lalu sidebar &gt; Mills Setting (/mill-settings).</t>
         </is>
       </c>
       <c r="K269" s="14" t="inlineStr">
         <is>
           <t>- Simpan berhasil dengan pesan konfirmasi.
 - Nilai baru bertahan sesudah muat ulang.
-- Nilai baru berlaku di layar yang memakainya.
-- Nilai yang tersimpan tapi tidak berpengaruh ke layar mana pun adalah separuh fitur — itu yang diperiksa di langkah 4–5.</t>
+- Nilai baru berlaku di aplikasi mobile — nama baru itu yang tampil di Home.
+- Nilai yang tersimpan tapi tidak berpengaruh ke layar mana pun adalah separuh fitur — itu yang
+diperiksa di langkah 4–5.</t>
         </is>
       </c>
       <c r="L269" s="11" t="inlineStr">
         <is>
-          <t>Sedang ---</t>
-        </is>
-      </c>
-      <c r="M269" s="14" t="inlineStr"/>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="M269" s="14" t="inlineStr">
+        <is>
+          <t>Catatan jalan: seluruh pengaturan di layar ini dipakai aplikasi mobile, bukan layar web mana pun — Nama Aplikasi dan Logo pada Home mobile, Gambar Halaman Utama, saklar kirim-langsung pada penyimpanan Operator, dan Icon Station pada daftar stasiun mobile. Jadi langkah 1–3 dijalankan di web, dan langkah 4–5 harus dijalankan di aplikasi mobile.
+pengaturan Jumlah Cages sudah tidak ada lagi di layar ini (jumlah cages kini diturunkan dari data mesin stasiun). Kalau Anda mencarinya karena pernah membacanya di versi dokumen lama, ketiadaannya bukan bug.</t>
+        </is>
+      </c>
       <c r="N269" s="17" t="n"/>
       <c r="O269" s="17" t="n"/>
       <c r="P269" s="17" t="n"/>
@@ -19987,8 +20080,8 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="P5:P269" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Nilai tidak dikenal" error="Pilih salah satu: Lulus, Gagal, Tidak diuji, Terhalang." type="list">
-      <formula1>"Lulus,Gagal,Tidak diuji,Terhalang"</formula1>
+    <dataValidation sqref="P5:P104 P109:P118 P122:P269" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Nilai tidak dikenal" error="Pilih salah satu: Lulus, Gagal, Tidak diuji, Tidak berlaku, Terhalang." type="list">
+      <formula1>"Lulus,Gagal,Tidak diuji,Tidak berlaku,Terhalang"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20077,305 +20170,305 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Aturan lintas-sistem</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>LS-</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"LS-*",'Kasus Uji'!$P$5:$P$269,"Lulus")</f>
         <v/>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"LS-*",'Kasus Uji'!$P$5:$P$269,"Gagal")</f>
         <v/>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"LS-*",'Kasus Uji'!$P$5:$P$269,"Tidak diuji")</f>
         <v/>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"LS-*",'Kasus Uji'!$P$5:$P$269,"Terhalang")</f>
         <v/>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="27">
         <f>D5-E5-F5-G5-H5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Autentikasi &amp; Akun</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>AU-</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"AU-*",'Kasus Uji'!$P$5:$P$269,"Lulus")</f>
         <v/>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"AU-*",'Kasus Uji'!$P$5:$P$269,"Gagal")</f>
         <v/>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"AU-*",'Kasus Uji'!$P$5:$P$269,"Tidak diuji")</f>
         <v/>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"AU-*",'Kasus Uji'!$P$5:$P$269,"Terhalang")</f>
         <v/>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="27">
         <f>D6-E6-F6-G6-H6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Mobile — Operasional Stasiun</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>MB-</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="27" t="n">
         <v>39</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="27" t="n">
         <v>73</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"MB-*",'Kasus Uji'!$P$5:$P$269,"Lulus")</f>
         <v/>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"MB-*",'Kasus Uji'!$P$5:$P$269,"Gagal")</f>
         <v/>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"MB-*",'Kasus Uji'!$P$5:$P$269,"Tidak diuji")</f>
         <v/>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"MB-*",'Kasus Uji'!$P$5:$P$269,"Terhalang")</f>
         <v/>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="27">
         <f>D7-E7-F7-G7-H7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Web — Data Stasiun</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>WB-</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="27" t="n">
         <v>76</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"WB-*",'Kasus Uji'!$P$5:$P$269,"Lulus")</f>
         <v/>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"WB-*",'Kasus Uji'!$P$5:$P$269,"Gagal")</f>
         <v/>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"WB-*",'Kasus Uji'!$P$5:$P$269,"Tidak diuji")</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"WB-*",'Kasus Uji'!$P$5:$P$269,"Terhalang")</f>
         <v/>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="27">
         <f>D8-E8-F8-G8-H8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Laporan Periode Stasiun</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>LP-</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="27" t="n">
         <v>41</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"LP-*",'Kasus Uji'!$P$5:$P$269,"Lulus")</f>
         <v/>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"LP-*",'Kasus Uji'!$P$5:$P$269,"Gagal")</f>
         <v/>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"LP-*",'Kasus Uji'!$P$5:$P$269,"Tidak diuji")</f>
         <v/>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"LP-*",'Kasus Uji'!$P$5:$P$269,"Terhalang")</f>
         <v/>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="27">
         <f>D9-E9-F9-G9-H9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Dashboard &amp; Laporan lain</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>DS-</t>
         </is>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"DS-*",'Kasus Uji'!$P$5:$P$269,"Lulus")</f>
         <v/>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"DS-*",'Kasus Uji'!$P$5:$P$269,"Gagal")</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"DS-*",'Kasus Uji'!$P$5:$P$269,"Tidak diuji")</f>
         <v/>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"DS-*",'Kasus Uji'!$P$5:$P$269,"Terhalang")</f>
         <v/>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="27">
         <f>D10-E10-F10-G10-H10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Master Data</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>MD-</t>
         </is>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="27" t="n">
         <v>28</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="27" t="n">
         <v>28</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"MD-*",'Kasus Uji'!$P$5:$P$269,"Lulus")</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"MD-*",'Kasus Uji'!$P$5:$P$269,"Gagal")</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"MD-*",'Kasus Uji'!$P$5:$P$269,"Tidak diuji")</f>
         <v/>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"MD-*",'Kasus Uji'!$P$5:$P$269,"Terhalang")</f>
         <v/>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="27">
         <f>D11-E11-F11-G11-H11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>User &amp; Role, Pengaturan Mill</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>AD-</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"AD-*",'Kasus Uji'!$P$5:$P$269,"Lulus")</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"AD-*",'Kasus Uji'!$P$5:$P$269,"Gagal")</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"AD-*",'Kasus Uji'!$P$5:$P$269,"Tidak diuji")</f>
         <v/>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="27">
         <f>COUNTIFS('Kasus Uji'!$D$5:$D$269,"AD-*",'Kasus Uji'!$P$5:$P$269,"Terhalang")</f>
         <v/>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="27">
         <f>D12-E12-F12-G12-H12</f>
         <v/>
       </c>
@@ -20386,38 +20479,38 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr"/>
-      <c r="C13" s="27">
+      <c r="B13" s="28" t="inlineStr"/>
+      <c r="C13" s="29">
         <f>SUM(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="29">
         <f>SUM(D5:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="29">
         <f>SUM(E5:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="29">
         <f>SUM(F5:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="29">
         <f>SUM(G5:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="29">
         <f>SUM(H5:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="29">
         <f>SUM(I5:I12)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>Kasus Prioritas Tinggi yang belum diisi</t>
         </is>
@@ -20430,7 +20523,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>Baris Gagal yang belum punya No. Bug</t>
         </is>
@@ -20561,41 +20654,41 @@
       <c r="I21" s="18" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>SISA — pengulangan penuh. Untuk putaran rilis atau saat satu stasiun berubah.</t>
         </is>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="28">
         <f>COUNTIFS('Kasus Uji'!$B$5:$B$269,3,'Kasus Uji'!$P$5:$P$269,"Lulus")</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="28">
         <f>COUNTIFS('Kasus Uji'!$B$5:$B$269,3,'Kasus Uji'!$P$5:$P$269,"Gagal")</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="28">
         <f>COUNTIFS('Kasus Uji'!$B$5:$B$269,3,'Kasus Uji'!$P$5:$P$269,"Tidak diuji")</f>
         <v/>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="28">
         <f>COUNTIFS('Kasus Uji'!$B$5:$B$269,3,'Kasus Uji'!$P$5:$P$269,"Terhalang")</f>
         <v/>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="28">
         <f>C22-D22-E22-F22-G22</f>
         <v/>
       </c>
-      <c r="I22" s="26" t="inlineStr"/>
+      <c r="I22" s="28" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>Tingkat 1+2</t>
         </is>
@@ -20605,30 +20698,30 @@
           <t>Cakupan yang masuk akal untuk pengujian manual satu putaran.</t>
         </is>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="29" t="n">
         <v>265</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="29">
         <f>SUM(D20:D21)</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="29">
         <f>SUM(E20:E21)</f>
         <v/>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="29">
         <f>SUM(F20:F21)</f>
         <v/>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="29">
         <f>SUM(G20:G21)</f>
         <v/>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="29">
         <f>SUM(H20:H21)</f>
         <v/>
       </c>
-      <c r="I23" s="26" t="inlineStr"/>
+      <c r="I23" s="28" t="inlineStr"/>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
@@ -20713,7 +20806,7 @@
       <c r="F5" s="7" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Aplikasi Web</t>
         </is>
@@ -20729,12 +20822,12 @@
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Aplikasi Mobile</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Dibuka di perangkat atau emulator. Lebar acuan 390px.</t>
         </is>
@@ -20745,7 +20838,7 @@
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Koneksi</t>
         </is>
@@ -20761,12 +20854,12 @@
       <c r="F8" s="7" t="n"/>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Data master</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Minimal: 1 Corporate, 1 Company, 2 Mill, masing-masing 2 Production Line, dan stasiun aktif untuk ke-18 jenis.</t>
         </is>
@@ -20777,7 +20870,7 @@
       <c r="F9" s="7" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Periode Pelaporan</t>
         </is>
@@ -20824,7 +20917,7 @@
       <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>OPR-A</t>
         </is>
@@ -20848,22 +20941,22 @@
       <c r="F14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>SPV-A</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>Mill A</t>
         </is>
       </c>
-      <c r="D15" s="31" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>Input + verifikasi "Checked"</t>
         </is>
@@ -20872,7 +20965,7 @@
       <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>MGR-A</t>
         </is>
@@ -20896,22 +20989,22 @@
       <c r="F16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>SPV-B</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>Mill B</t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>Menguji data Mill A tidak terlihat</t>
         </is>
@@ -20920,7 +21013,7 @@
       <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>ADM</t>
         </is>
@@ -20944,22 +21037,22 @@
       <c r="F18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>NOMILL</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="C19" s="30" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
         <is>
           <t>tanpa mill</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>Menguji sistem menolak dengan jelas</t>
         </is>
@@ -21019,27 +21112,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Login Mobile</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -21051,59 +21144,59 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>Login Web</t>
         </is>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>v terbatas</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D25" s="34" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E25" s="34" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr">
+      <c r="F25" s="32" t="inlineStr">
         <is>
           <t>Operator: hanya 3 layar, lihat baris terbawah</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Input data stasiun (Mobile)</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E26" s="35" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -21111,55 +21204,55 @@
       <c r="F26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Input data stasiun (Web)</t>
         </is>
       </c>
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="D27" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E27" s="34" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F27" s="31" t="inlineStr"/>
+      <c r="F27" s="32" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Isi Checked By</t>
         </is>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D28" s="35" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -21167,55 +21260,55 @@
       <c r="F28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>Isi Acknowledged By</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="34" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E29" s="34" t="inlineStr">
+      <c r="E29" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr"/>
+      <c r="F29" s="32" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Lihat Data Browser / Detail (Web)</t>
         </is>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -21223,55 +21316,55 @@
       <c r="F30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>Lihat "Data Saya" (Web)</t>
         </is>
       </c>
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D31" s="35" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="31" t="inlineStr"/>
+      <c r="F31" s="32" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>Laporan periode stasiun (Web)</t>
         </is>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -21279,55 +21372,55 @@
       <c r="F32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>Laporan periode stasiun (Mobile)</t>
         </is>
       </c>
-      <c r="B33" s="34" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C33" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D33" s="34" t="inlineStr">
+      <c r="D33" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E33" s="34" t="inlineStr">
+      <c r="E33" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F33" s="31" t="inlineStr"/>
+      <c r="F33" s="32" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>Dashboard (Web)</t>
         </is>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E34" s="25" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -21335,55 +21428,55 @@
       <c r="F34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>Laporan Manajemen</t>
         </is>
       </c>
-      <c r="B35" s="35" t="inlineStr">
+      <c r="B35" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D35" s="34" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E35" s="34" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr"/>
+      <c r="F35" s="32" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>Master data (Corporate…Mesin)</t>
         </is>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr">
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -21391,115 +21484,115 @@
       <c r="F36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>Periode Pelaporan: tambah/ubah/hapus</t>
         </is>
       </c>
-      <c r="B37" s="35" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D37" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="34" t="inlineStr">
+      <c r="E37" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F37" s="31" t="inlineStr"/>
+      <c r="F37" s="32" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>Tutup / Buka Periode</t>
         </is>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr">
+      <c r="C38" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="35" t="inlineStr">
+      <c r="D38" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F38" s="36" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>HANYA Admin</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="inlineStr">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Pengaturan Mill</t>
         </is>
       </c>
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C39" s="35" t="inlineStr">
+      <c r="C39" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D39" s="34" t="inlineStr">
+      <c r="D39" s="35" t="inlineStr">
         <is>
           <t>v mill sendiri</t>
         </is>
       </c>
-      <c r="E39" s="34" t="inlineStr">
+      <c r="E39" s="35" t="inlineStr">
         <is>
           <t>v semua mill</t>
         </is>
       </c>
-      <c r="F39" s="31" t="inlineStr"/>
+      <c r="F39" s="32" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>Kelola User &amp; Role</t>
         </is>
       </c>
-      <c r="B40" s="35" t="inlineStr">
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C40" s="35" t="inlineStr">
+      <c r="C40" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D40" s="35" t="inlineStr">
+      <c r="D40" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -21507,32 +21600,32 @@
       <c r="F40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>Pemilih Mill pada laporan</t>
         </is>
       </c>
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B41" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C41" s="35" t="inlineStr">
+      <c r="C41" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D41" s="35" t="inlineStr">
+      <c r="D41" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E41" s="34" t="inlineStr">
+      <c r="E41" s="35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F41" s="37" t="inlineStr">
+      <c r="F41" s="38" t="inlineStr">
         <is>
           <t>HANYA Admin</t>
         </is>
@@ -21647,10 +21740,10 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="25" t="n">
+      <c r="A5" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Weighbridge</t>
         </is>
@@ -21660,17 +21753,17 @@
           <t>No. Kartu / Kendaraan</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>per-transaksi</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>Per-transaksi</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
@@ -21682,45 +21775,45 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Grading</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Parameter grading</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>per-muatan</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>Per-transaksi</t>
         </is>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Satu record per muatan, ada beberapa baris parameter</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Cages Track</t>
         </is>
@@ -21730,17 +21823,17 @@
           <t>ID Cage</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>±</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
@@ -21748,45 +21841,45 @@
       <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Sterilizer</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>ID Sterilizer</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>±</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F8" s="34" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
       </c>
-      <c r="G8" s="31" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Ada checkbox "Checked by SPV" per baris — Operator tidak boleh bisa mengisinya</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Threshing</t>
         </is>
@@ -21796,17 +21889,17 @@
           <t>ID Thresher</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
@@ -21818,45 +21911,45 @@
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Pressing</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>ID Presser</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F10" s="34" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
       </c>
-      <c r="G10" s="31" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Punya master target</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
@@ -21866,17 +21959,17 @@
           <t>ID unit</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>±</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
@@ -21884,45 +21977,45 @@
       <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="34" t="n">
+      <c r="A12" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>Kernel Plant</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>ID unit kernel plant</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
       </c>
-      <c r="G12" s="31" t="inlineStr">
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t>Punya master target. Dua pasang kolom berbagi satu standar (2 ripple mill, 2 kernel silo)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="25" t="n">
+      <c r="A13" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Boiler Room</t>
         </is>
@@ -21932,17 +22025,17 @@
           <t>ID boiler</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>±</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
@@ -21950,45 +22043,45 @@
       <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="34" t="n">
+      <c r="A14" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Effluent Plant</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>ID unit</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F14" s="38" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>BELUM dibangun</t>
         </is>
       </c>
-      <c r="G14" s="31" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>PALING BANYAK KOLOM. Ada 3 kolom status pilihan (on/off/fault, run/stop) dan 2 kolom teks bebas</t>
         </is>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Depricarping</t>
         </is>
@@ -21998,17 +22091,17 @@
           <t>ID Presser</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
@@ -22020,41 +22113,41 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="34" t="n">
+      <c r="A16" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>Engine Room</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>ID unit</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>±</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F16" s="38" t="inlineStr">
+      <c r="F16" s="39" t="inlineStr">
         <is>
           <t>Belum</t>
         </is>
       </c>
-      <c r="G16" s="31" t="inlineStr"/>
+      <c r="G16" s="32" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Process Water</t>
         </is>
@@ -22064,17 +22157,17 @@
           <t>ID unit</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>±</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F17" s="39" t="inlineStr">
+      <c r="F17" s="40" t="inlineStr">
         <is>
           <t>Belum</t>
         </is>
@@ -22086,41 +22179,41 @@
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="34" t="n">
+      <c r="A18" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>Storage Tank</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>ID tangki</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>±</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F18" s="34" t="inlineStr">
+      <c r="F18" s="35" t="inlineStr">
         <is>
           <t>Ada (web+mobile)</t>
         </is>
       </c>
-      <c r="G18" s="31" t="inlineStr"/>
+      <c r="G18" s="32" t="inlineStr"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Solid Waste Disposal</t>
         </is>
@@ -22130,17 +22223,17 @@
           <t>ID unit</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>±</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F19" s="39" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>Belum</t>
         </is>
@@ -22148,45 +22241,45 @@
       <c r="G19" s="5" t="inlineStr"/>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="34" t="n">
+      <c r="A20" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>Kernel Dispatch</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
         <is>
           <t>No. Kartu / Kendaraan</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>per-transaksi</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>Per-transaksi</t>
         </is>
       </c>
-      <c r="F20" s="38" t="inlineStr">
+      <c r="F20" s="39" t="inlineStr">
         <is>
           <t>Belum</t>
         </is>
       </c>
-      <c r="G20" s="31" t="inlineStr">
+      <c r="G20" s="32" t="inlineStr">
         <is>
           <t>Pola per-transaksi, ada kolom status pilihan</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="25" t="n">
+      <c r="A21" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>CPO Dispatch</t>
         </is>
@@ -22196,17 +22289,17 @@
           <t>No. Kartu / Kendaraan</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>per-transaksi</t>
         </is>
       </c>
-      <c r="E21" s="35" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>Per-transaksi</t>
         </is>
       </c>
-      <c r="F21" s="39" t="inlineStr">
+      <c r="F21" s="40" t="inlineStr">
         <is>
           <t>Belum</t>
         </is>
@@ -22218,35 +22311,35 @@
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="35" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>Process Quality Control</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>ID unit</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>±</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>24 slot</t>
         </is>
       </c>
-      <c r="F22" s="38" t="inlineStr">
+      <c r="F22" s="39" t="inlineStr">
         <is>
           <t>Belum</t>
         </is>
       </c>
-      <c r="G22" s="31" t="inlineStr"/>
+      <c r="G22" s="32" t="inlineStr"/>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -22321,7 +22414,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>Hal-hal di bawah sudah diketahui dan bukan temuan baru. Kalau penguji menemukannya, cukup rujuk nomornya alih-alih membuat laporan bug baru.</t>
         </is>
@@ -22345,12 +22438,12 @@
       </c>
     </row>
     <row r="7" ht="83.19999999999999" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>B-1</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Laporan periode belum tersedia untuk 7 stasiun</t>
         </is>
@@ -22362,29 +22455,29 @@
       </c>
     </row>
     <row r="8" ht="56.8" customHeight="1">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>B-2</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Layar "Data Saya" belum tersedia</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Daftar record yang dibuat pengguna itu sendiri belum ada. Akibatnya akses web untuk peran Station Operator terbatas pada dua layar: Beranda Operator dan Ganti Password. Operator tetap dapat menginput lewat aplikasi mobile seperti biasa.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="96.39999999999999" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>B-3</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Dashboard adalah tampilan contoh, bukan laporan mill</t>
         </is>
@@ -22396,29 +22489,29 @@
       </c>
     </row>
     <row r="10" ht="43.59999999999999" customHeight="1">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>B-4</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Satuan suhu ditulis "C", bukan "°C"</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Pada laporan Kernel Plant, web maupun mobile. Disengaja: satuannya mengikuti data master apa adanya, dan mengubahnya di tampilan akan membuat web dan mobile berselisih.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.4" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>B-5</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Laporan Depricarping (Mobile): tiga angka pada blok downtime tampil tanpa gaya</t>
         </is>
@@ -22454,7 +22547,7 @@
       </c>
     </row>
     <row r="16" ht="40.5" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>LS-16</t>
         </is>
@@ -22464,31 +22557,31 @@
           <t>Laporan tidak menandai nilai yang jelas di luar batas</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>DISENGAJA. Kolom targetnya teks bebas yang bentuknya tidak dibatasi, dan satu sel bisa memuat dua angka dengan satuan berbeda. Ada kalimat di layar yang menjelaskannya.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>MB-FORM-04</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Slot waktu 01:00 dianggap SESUDAH 23:00</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>BENAR. Shift dimulai 07:00, jadi urutannya 07:00 → 23:00 → 00:00 → 06:00.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40.5" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>DS-02</t>
         </is>
@@ -22498,31 +22591,31 @@
           <t>Dashboard menampilkan angka yang sama untuk semua peran dan semua mill</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>BENAR. Halaman itu tampilan contoh dengan angka tetap, dan menyatakannya lewat penanda "Data dummy". Jangan jalankan uji isolasi mill di sana — ia tidak membaca mill sama sekali.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40.5" customHeight="1">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>DS-10</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Satu stasiun menunjukkan "belum ada input hari ini" DAN "input terakhir 3 menit lalu"</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>BENAR. Dua jendela waktu yang berbeda: "hari ini" dibatasi tanggal, "input terakhir" tidak. Keterangan di halaman menjelaskannya.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>LP-W-05</t>
         </is>
@@ -22532,31 +22625,31 @@
           <t>Persen cakupan 0,0% di satu periode dan tanda pisah di periode lain, keduanya "tanpa data"</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>BENAR, DAN KEDUANYA BERBEDA. 0,0% = penyebutnya ada, nol yang terisi. Tanda pisah = penyebutnya tidak terbentuk.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>LP-W-03</t>
         </is>
       </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Jumlah slot terisi pada cakupan LEBIH BESAR daripada penyebut parameter mana pun</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>BENAR. Slot yang hanya mengisi kolom temuan terhitung terisi tanpa menambah penyebut parameter.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>LS-08</t>
         </is>
@@ -22566,7 +22659,7 @@
           <t>Production Line tunggal tetap harus dipilih manual</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>DISENGAJA. Memilihnya otomatis membuat pembaca mengira ia melihat seluruh mill.</t>
         </is>

--- a/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
@@ -19428,7 +19428,7 @@
       <c r="Q260" s="17" t="n"/>
       <c r="R260" s="17" t="n"/>
     </row>
-    <row r="261" ht="294.4" customHeight="1">
+    <row r="261" ht="439.6" customHeight="1">
       <c r="A261" s="11" t="n">
         <v>257</v>
       </c>
@@ -19476,7 +19476,8 @@
 2. Ubah nilai itu, tekan Simpan.
 3. Muat ulang halaman (F5). Baca nilainya.
 4. Login di mobile (buka aplikasi, isi username dan password, tekan Login), mendarat di /home sebagai OPR-A pada mill yang sama, lalu sinkronkan bila diminta.
-5. Baca nama aplikasi yang tampil di layar Home mobile.
+5. Periksa bahwa nilai baru itu sudah ada di perangkat (tersinkron), lalu baca baris merek
+pada layar Home mobile.
 6. Kembalikan nilainya ke semula lewat Login di web, lalu sidebar &gt; Mills Setting (/mill-settings).</t>
         </is>
       </c>
@@ -19484,9 +19485,12 @@
         <is>
           <t>- Simpan berhasil dengan pesan konfirmasi.
 - Nilai baru bertahan sesudah muat ulang.
-- Nilai baru berlaku di aplikasi mobile — nama baru itu yang tampil di Home.
-- Nilai yang tersimpan tapi tidak berpengaruh ke layar mana pun adalah separuh fitur — itu yang
-diperiksa di langkah 4–5.</t>
+- Nilai baru sampai ke perangkat sesudah sinkronisasi — itu yang diperiksa langkah 4–5:
+jalur simpan → kirim → simpan di perangkat bekerja utuh.
+- Baris merek pada Home mobile tetap nama produk, TIDAK berubah mengikuti Nama Aplikasi.
+Itu bukan kegagalan: nama produk pada header memang terpisah dari Nama Aplikasi per mill.
+- Terbuka, dan bukan bagian dari kasus ini: Nama Aplikasi dan Logo saat ini tersimpan dan
+tersinkron tetapi belum dibaca layar mana pun. Keduanya menunggu layar yang memakainya.</t>
         </is>
       </c>
       <c r="L261" s="11" t="inlineStr">
@@ -19496,7 +19500,7 @@
       </c>
       <c r="M261" s="14" t="inlineStr">
         <is>
-          <t>Catatan jalan: seluruh pengaturan di layar ini dipakai aplikasi mobile, bukan layar web mana pun — Nama Aplikasi dan Logo pada Home mobile, Gambar Halaman Utama, saklar kirim-langsung pada penyimpanan Operator, dan Icon Station pada daftar stasiun mobile. Jadi langkah 1–3 dijalankan di web, dan langkah 4–5 harus dijalankan di aplikasi mobile.
+          <t>Catatan jalan: pengaturan di layar ini dipakai aplikasi mobile, bukan layar web mana pun — Gambar Halaman Utama pada Home mobile, saklar kirim-langsung pada penyimpanan Operator, dan Icon Station pada daftar stasiun mobile. Nama Aplikasi dan Logo adalah pengecualian: keduanya belum dibaca satu layar pun. Baris merek pada Home mobile memakai nama produk yang tetap, dan itu keputusan yang disengaja — nama produk pada header terpisah dari Nama Aplikasi per mill. Jadi langkah 1–3 dijalankan di web, dan langkah 4–5 harus dijalankan di aplikasi mobile untuk memeriksa bahwa nilainya sampai ke perangkat, bukan bahwa ia tampil di Home.
 pengaturan Jumlah Cages sudah tidak ada lagi di layar ini (jumlah cages kini diturunkan dari data mesin stasiun). Kalau Anda mencarinya karena pernah membacanya di versi dokumen lama, ketiadaannya bukan bug.</t>
         </is>
       </c>

--- a/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
@@ -690,7 +690,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mill Smart Log — Test Case Blackbox (ALUR — Tingkat 1+2)</t>
+          <t>Mills Smart Log — Test Case Blackbox (ALUR — Tingkat 1+2)</t>
         </is>
       </c>
     </row>

--- a/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Test-Case-Blackbox-Alur.xlsx
@@ -19428,7 +19428,7 @@
       <c r="Q260" s="17" t="n"/>
       <c r="R260" s="17" t="n"/>
     </row>
-    <row r="261" ht="439.6" customHeight="1">
+    <row r="261" ht="545.1999999999999" customHeight="1">
       <c r="A261" s="11" t="n">
         <v>257</v>
       </c>
@@ -19472,25 +19472,23 @@
       </c>
       <c r="J261" s="14" t="inlineStr">
         <is>
-          <t>1. Login di web, lalu sidebar &gt; Mills Setting (/mill-settings) sebagai MGR-A. Catat nilai awal Nama Aplikasi.
-2. Ubah nilai itu, tekan Simpan.
-3. Muat ulang halaman (F5). Baca nilainya.
+          <t>1. Login di web, lalu sidebar &gt; Mills Setting (/mill-settings) sebagai MGR-A. Catat posisi awal saklar "Kirim data langsung ke server saat
+disimpan" (aktif / nonaktif).
+2. Ubah posisinya, tekan Simpan.
+3. Muat ulang halaman (F5). Baca posisinya.
 4. Login di mobile (buka aplikasi, isi username dan password, tekan Login), mendarat di /home sebagai OPR-A pada mill yang sama, lalu sinkronkan bila diminta.
-5. Periksa bahwa nilai baru itu sudah ada di perangkat (tersinkron), lalu baca baris merek
-pada layar Home mobile.
-6. Kembalikan nilainya ke semula lewat Login di web, lalu sidebar &gt; Mills Setting (/mill-settings).</t>
+5. Periksa bahwa posisi baru itu sudah ada di perangkat (tersinkron).
+6. Kembalikan posisinya ke semula lewat Login di web, lalu sidebar &gt; Mills Setting (/mill-settings).</t>
         </is>
       </c>
       <c r="K261" s="14" t="inlineStr">
         <is>
           <t>- Simpan berhasil dengan pesan konfirmasi.
-- Nilai baru bertahan sesudah muat ulang.
-- Nilai baru sampai ke perangkat sesudah sinkronisasi — itu yang diperiksa langkah 4–5:
+- Posisi baru bertahan sesudah muat ulang.
+- Posisi baru sampai ke perangkat sesudah sinkronisasi — itu yang diperiksa langkah 4–5:
 jalur simpan → kirim → simpan di perangkat bekerja utuh.
-- Baris merek pada Home mobile tetap nama produk, TIDAK berubah mengikuti Nama Aplikasi.
-Itu bukan kegagalan: nama produk pada header memang terpisah dari Nama Aplikasi per mill.
-- Terbuka, dan bukan bagian dari kasus ini: Nama Aplikasi dan Logo saat ini tersimpan dan
-tersinkron tetapi belum dibaca layar mana pun. Keduanya menunggu layar yang memakainya.</t>
+- Nilai yang tersimpan tapi tidak berpengaruh ke layar atau perilaku mana pun adalah separuh
+fitur — itu yang dijaga kasus ini.</t>
         </is>
       </c>
       <c r="L261" s="11" t="inlineStr">
@@ -19500,8 +19498,8 @@
       </c>
       <c r="M261" s="14" t="inlineStr">
         <is>
-          <t>Catatan jalan: pengaturan di layar ini dipakai aplikasi mobile, bukan layar web mana pun — Gambar Halaman Utama pada Home mobile, saklar kirim-langsung pada penyimpanan Operator, dan Icon Station pada daftar stasiun mobile. Nama Aplikasi dan Logo adalah pengecualian: keduanya belum dibaca satu layar pun. Baris merek pada Home mobile memakai nama produk yang tetap, dan itu keputusan yang disengaja — nama produk pada header terpisah dari Nama Aplikasi per mill. Jadi langkah 1–3 dijalankan di web, dan langkah 4–5 harus dijalankan di aplikasi mobile untuk memeriksa bahwa nilainya sampai ke perangkat, bukan bahwa ia tampil di Home.
-pengaturan Jumlah Cages sudah tidak ada lagi di layar ini (jumlah cages kini diturunkan dari data mesin stasiun). Kalau Anda mencarinya karena pernah membacanya di versi dokumen lama, ketiadaannya bukan bug.</t>
+          <t>Catatan jalan: setiap pengaturan di layar ini dipakai aplikasi mobile, bukan layar web mana pun — Gambar Halaman Utama pada Home mobile, saklar "Kirim data langsung ke server saat disimpan" pada penyimpanan Operator, dan Icon Station pada daftar stasiun mobile. Jadi langkah 1–3 dijalankan di web, dan langkah 4–5 harus dijalankan di aplikasi mobile. Yang dipakai kasus ini adalah saklar kirim-langsung. Saklar itu tidak ditampilkan di layar mobile mana pun — ia mengubah perilaku penyimpanan — jadi yang diperiksa pada langkah 5 adalah nilainya sampai ke perangkat, bukan sesuatu yang tertulis di layar.
+tiga pengaturan sudah tidak ada lagi di layar ini, dan ketiadaannya bukan bug. Jumlah Cages — jumlah cages kini diturunkan dari data mesin stasiun. Nama Aplikasi dan Logo — tidak ada satu layar pun yang membacanya: baris merek pada Home mobile memakai nama produk yang tetap, terpisah dari nama aplikasi per mill. Kalau Anda mencari ketiganya karena pernah membacanya di versi dokumen lama, ketiganya memang sudah dicabut.</t>
         </is>
       </c>
       <c r="N261" s="17" t="n"/>
